--- a/output/pdf_financials_xlsx/KORE.xlsx
+++ b/output/pdf_financials_xlsx/KORE.xlsx
@@ -1342,7 +1342,7 @@
         <v>-0.46368</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>1.296244</v>
+        <v>-1.296244</v>
       </c>
       <c r="L16" s="3" t="n">
         <v>-4.505122</v>
@@ -1650,7 +1650,7 @@
         <v>-0.46368</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>1.296244</v>
+        <v>-1.296244</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>-4.505122</v>
@@ -1836,7 +1836,7 @@
         <v>-0.46368</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>1.296244</v>
+        <v>-1.296244</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>-4.505122</v>
@@ -2052,7 +2052,7 @@
         <v>25.76</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-72.01355599999999</v>
+        <v>72.01355599999999</v>
       </c>
       <c r="L26" s="1" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>-0.46368</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>1.296244</v>
+        <v>-1.296244</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>-4.505122</v>
@@ -2248,7 +2248,7 @@
         <v>-0.46368</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>1.296244</v>
+        <v>-1.296244</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>-4.505122</v>
@@ -2402,7 +2402,7 @@
         <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>-0</v>
@@ -6035,10 +6035,10 @@
         <v>0.447156</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.447156</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.447156</v>
       </c>
       <c r="I92" s="3" t="n">
         <v>0</v>
@@ -6050,25 +6050,25 @@
         <v>0</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.341739</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.878946</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>2.531798</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>3.082196</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>3.268196</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>3.326782</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>3.345138</v>
       </c>
     </row>
     <row r="93">
@@ -10054,7 +10054,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -12127,7 +12131,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -15594,7 +15602,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
@@ -22261,7 +22273,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
@@ -22863,7 +22879,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
           <t>-</t>
@@ -58417,7 +58437,7 @@
         </is>
       </c>
       <c r="N497" s="5" t="n">
-        <v>1.296244</v>
+        <v>-1.296244</v>
       </c>
       <c r="O497" s="5" t="n">
         <v>-4.505122</v>
@@ -58615,7 +58635,7 @@
         </is>
       </c>
       <c r="N499" s="5" t="n">
-        <v>1.337418</v>
+        <v>-1.337418</v>
       </c>
       <c r="O499" s="5" t="n">
         <v>-4.453641</v>

--- a/output/pdf_financials_xlsx/KORE.xlsx
+++ b/output/pdf_financials_xlsx/KORE.xlsx
@@ -987,13 +987,13 @@
         </is>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0</v>
+        <v>1.549191</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0</v>
+        <v>1.467442</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0</v>
+        <v>1.7962</v>
       </c>
     </row>
     <row r="11">
@@ -1051,13 +1051,13 @@
         </is>
       </c>
       <c r="P11" s="3" t="n">
-        <v>0</v>
+        <v>-1.549191</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>0</v>
+        <v>-1.467442</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>0</v>
+        <v>-1.7962</v>
       </c>
     </row>
     <row r="12">
@@ -1067,25 +1067,25 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>6.999999999999999e-05</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000114</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>6.9e-05</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.000132</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-2.9e-05</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-5.8e-05</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -2097,25 +2097,25 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.439875</v>
+        <v>-0.439945</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.039743</v>
+        <v>-0.039857</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.146881</v>
+        <v>-0.14695</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-0.692376</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.020479</v>
+        <v>-0.020611</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.059413</v>
+        <v>-0.059384</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.151996</v>
+        <v>-0.151938</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-0.46368</v>
@@ -2221,25 +2221,25 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.439875</v>
+        <v>-0.439945</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.039743</v>
+        <v>-0.039857</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.146881</v>
+        <v>-0.14695</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-0.692376</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.020479</v>
+        <v>-0.020611</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.059413</v>
+        <v>-0.059384</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.151996</v>
+        <v>-0.151938</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-0.46368</v>
@@ -2551,16 +2551,16 @@
         <v>0.072965</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.003108</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.003633</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.062679</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.392664</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>0.088694</v>
@@ -2581,10 +2581,10 @@
         <v>0.022211</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.00474</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.800407</v>
       </c>
     </row>
     <row r="35">
@@ -2667,16 +2667,16 @@
         <v>0.072965</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.003108</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.003633</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.062679</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.392664</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>0.088694</v>
@@ -2697,10 +2697,10 @@
         <v>0.022211</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.00474</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.800407</v>
       </c>
     </row>
     <row r="37">
@@ -3363,16 +3363,16 @@
         <v>0.00319</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.006317</v>
+        <v>0.003209</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.006842</v>
+        <v>0.003209</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.062679</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.470577</v>
+        <v>0.077913</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0</v>
@@ -3393,10 +3393,10 @@
         <v>0.013831</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.281608</v>
+        <v>0.276868</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>1.097019</v>
+        <v>0.296612</v>
       </c>
     </row>
     <row r="49">
@@ -8727,7 +8727,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -10571,7 +10571,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -18873,7 +18873,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -22778,7 +22778,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -54465,7 +54465,7 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
@@ -54544,10 +54544,10 @@
         </is>
       </c>
       <c r="T458" s="5" t="n">
-        <v>-1.467442</v>
+        <v>1.467442</v>
       </c>
       <c r="U458" s="5" t="n">
-        <v>-1.7962</v>
+        <v>1.7962</v>
       </c>
     </row>
     <row r="459">
@@ -54671,7 +54671,7 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
@@ -56172,7 +56172,7 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
@@ -56246,10 +56246,10 @@
         </is>
       </c>
       <c r="S475" s="5" t="n">
-        <v>-1.549191</v>
+        <v>1.549191</v>
       </c>
       <c r="T475" s="5" t="n">
-        <v>-1.467442</v>
+        <v>1.467442</v>
       </c>
       <c r="U475" t="inlineStr">
         <is>
@@ -56584,7 +56584,7 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
@@ -63104,7 +63104,7 @@
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E545" s="5" t="n">
@@ -63872,7 +63872,7 @@
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E553" s="5" t="n">

--- a/output/pdf_financials_xlsx/KORE.xlsx
+++ b/output/pdf_financials_xlsx/KORE.xlsx
@@ -773,13 +773,13 @@
         <v>0.02552</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.004714</v>
+        <v>0.024254</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.003123</v>
+        <v>0.04681</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.025528</v>
+        <v>0.121728</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0.026221</v>
@@ -897,10 +897,10 @@
         <v>0.004889</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0.014174</v>
+        <v>0.019747</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0.056344</v>
+        <v>0.07781299999999999</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>0.179482</v>
@@ -2618,7 +2618,7 @@
         <v>0</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0</v>
+        <v>0.02875</v>
       </c>
       <c r="K35" s="3" t="n">
         <v>0</v>
@@ -2676,7 +2676,7 @@
         <v>0.062679</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.392664</v>
+        <v>0.421414</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>0.088694</v>
@@ -3372,7 +3372,7 @@
         <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.077913</v>
+        <v>0.049163</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0</v>
@@ -3986,10 +3986,10 @@
         <v>0.096124</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0</v>
+        <v>0.283921</v>
       </c>
       <c r="K58" s="3" t="n">
-        <v>0</v>
+        <v>1.168164</v>
       </c>
       <c r="L58" s="3" t="n">
         <v>0</v>
@@ -4160,10 +4160,10 @@
         <v>0.005</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.301133</v>
+        <v>0.017212</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>0.690038</v>
+        <v>0</v>
       </c>
       <c r="L61" s="3" t="n">
         <v>1.622792</v>
@@ -4455,13 +4455,13 @@
         <v>0.304501</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>0</v>
+        <v>0.049782</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0</v>
+        <v>0.000395</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>0</v>
+        <v>0.290397</v>
       </c>
       <c r="L66" s="3" t="n">
         <v>0</v>
@@ -5805,10 +5805,10 @@
         <v>5.301469</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0</v>
+        <v>5.450446</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>0</v>
+        <v>6.439649</v>
       </c>
       <c r="K88" s="3" t="n">
         <v>2.546807</v>
@@ -6041,13 +6041,13 @@
         <v>0.447156</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.559156</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.741431</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.938536</v>
       </c>
       <c r="L92" s="3" t="n">
         <v>0.341739</v>
@@ -18968,7 +18968,11 @@
           <t>Restricted cash – Note 9</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
@@ -19069,7 +19073,11 @@
           <t>Marketable securities – Note 5</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>ShortTermInvestments</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
@@ -19568,7 +19576,11 @@
           <t>Exploration and evaluation assets – Notes 6 and 10</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>
@@ -19766,7 +19778,11 @@
           <t>Due to related parties – Note 10</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
           <t>-</t>
@@ -19960,7 +19976,11 @@
           <t>Share capital – Note 9</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>-</t>
@@ -20057,7 +20077,11 @@
           <t>Reserves – Note 9</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
@@ -20558,7 +20582,11 @@
           <t>Exploration and evaluation assets – Notes 6 and 14</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
           <t>-</t>
@@ -20964,7 +20992,11 @@
           <t>Share capital – Note 8</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
           <t>-</t>
@@ -21063,7 +21095,11 @@
           <t>Reserves – Note 8</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
           <t>-</t>
@@ -59374,7 +59410,11 @@
           <t>Consulting fees – Note 10</t>
         </is>
       </c>
-      <c r="D507" t="inlineStr"/>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E507" t="inlineStr">
         <is>
           <t>-</t>
@@ -59853,7 +59893,11 @@
           <t>Management fees – Note 10</t>
         </is>
       </c>
-      <c r="D512" t="inlineStr"/>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E512" t="inlineStr">
         <is>
           <t>-</t>
@@ -60156,7 +60200,11 @@
           <t>Rent – Note 10</t>
         </is>
       </c>
-      <c r="D515" t="inlineStr"/>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E515" t="inlineStr">
         <is>
           <t>-</t>
@@ -61738,7 +61786,11 @@
           <t>Office – Note 10</t>
         </is>
       </c>
-      <c r="D531" t="inlineStr"/>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E531" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/KORE.xlsx
+++ b/output/pdf_financials_xlsx/KORE.xlsx
@@ -755,22 +755,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.043782</v>
+        <v>0.044782</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.044386</v>
+        <v>0.045386</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0.042493</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.032443</v>
+        <v>0.033276</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.031557</v>
+        <v>0.033724</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.02552</v>
+        <v>0.028853</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>0.024254</v>
@@ -941,22 +941,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.049571</v>
+        <v>0.050571</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.049219</v>
+        <v>0.050219</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0.047419</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.03724</v>
+        <v>0.038073</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.036375</v>
+        <v>0.038542</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.030409</v>
+        <v>0.033742</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>0.083971</v>
@@ -1336,7 +1336,7 @@
         <v>-0.151996</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>-0.46368</v>
+        <v>0.08509899999999999</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>-0.46368</v>
@@ -1644,7 +1644,7 @@
         <v>-0.151996</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>-0.46368</v>
+        <v>0.08509899999999999</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>-0.46368</v>
@@ -1830,7 +1830,7 @@
         <v>-0.151996</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>-0.46368</v>
+        <v>0.08509899999999999</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>-0.46368</v>
@@ -2118,7 +2118,7 @@
         <v>-0.151938</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.46368</v>
+        <v>0.08509899999999999</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-0.46368</v>
@@ -2242,7 +2242,7 @@
         <v>-0.151938</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.46368</v>
+        <v>0.08509899999999999</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-0.46368</v>
@@ -2396,7 +2396,7 @@
         <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>-0</v>
@@ -4498,19 +4498,19 @@
         <v>0</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.018117</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.0102</v>
       </c>
       <c r="I67" s="3" t="n">
         <v>0</v>
@@ -6408,7 +6408,7 @@
         <v>-0.151996</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>-0.46368</v>
+        <v>0.08509899999999999</v>
       </c>
       <c r="J99" s="3" t="n">
         <v>-0.46368</v>
@@ -6529,10 +6529,10 @@
         <v>-0.004808</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>0</v>
+        <v>-0.005414</v>
       </c>
       <c r="K101" s="3" t="n">
-        <v>0</v>
+        <v>-0.009716000000000001</v>
       </c>
       <c r="L101" s="3" t="n">
         <v>0.005496</v>
@@ -6819,10 +6819,10 @@
         <v>0.046225</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>-0.02841</v>
+        <v>-0.033824</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0.31919</v>
+        <v>0.309474</v>
       </c>
       <c r="L106" s="3" t="n">
         <v>-1.901767</v>
@@ -7344,7 +7344,7 @@
         <v>0</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.02599</v>
       </c>
       <c r="L115" s="3" t="n">
         <v>0</v>
@@ -7506,7 +7506,7 @@
         <v>-0.021526</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>-0.025499</v>
+        <v>-0.050499</v>
       </c>
       <c r="H118" s="3" t="n">
         <v>0.068025</v>
@@ -8270,10 +8270,8 @@
       <c r="M130" s="3" t="n">
         <v>0.03062</v>
       </c>
-      <c r="N130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N130" s="3" t="n">
+        <v>4.906361</v>
       </c>
       <c r="O130" s="3" t="n">
         <v>3.592702</v>
@@ -8446,10 +8444,8 @@
       <c r="M133" s="3" t="n">
         <v>3.133623</v>
       </c>
-      <c r="N133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N133" s="3" t="n">
+        <v>3.592702</v>
       </c>
       <c r="O133" s="3" t="n">
         <v>0.743336</v>
@@ -8593,7 +8589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U562"/>
+  <dimension ref="A1:U567"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -29536,7 +29532,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E209" t="inlineStr">
         <is>
           <t>-</t>
@@ -35245,7 +35245,11 @@
           <t>Cash at beginning of the year</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr"/>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E266" t="inlineStr">
         <is>
           <t>-</t>
@@ -35344,7 +35348,11 @@
           <t>Cash at end of the year</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E267" t="inlineStr">
         <is>
           <t>-</t>
@@ -40083,7 +40091,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D314" t="inlineStr"/>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E314" t="inlineStr">
         <is>
           <t>-</t>
@@ -40863,10 +40875,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J322" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J322" s="5" t="n">
+        <v>-0.025499</v>
       </c>
       <c r="K322" t="inlineStr">
         <is>
@@ -40964,10 +40974,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J323" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J323" s="5" t="n">
+        <v>-0.000528</v>
       </c>
       <c r="K323" s="5" t="n">
         <v>0.000778</v>
@@ -41033,7 +41041,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr"/>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E324" t="inlineStr">
         <is>
           <t>-</t>
@@ -43364,7 +43376,11 @@
           <t>Private placements – Note 9 7,234,930 527,655 63,404</t>
         </is>
       </c>
-      <c r="D347" t="inlineStr"/>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E347" t="inlineStr">
         <is>
           <t>-</t>
@@ -46269,7 +46285,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D376" t="inlineStr"/>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E376" t="inlineStr">
         <is>
           <t>-</t>
@@ -48927,10 +48947,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J402" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J402" s="5" t="n">
+        <v>-2.9e-05</v>
       </c>
       <c r="K402" s="5" t="n">
         <v>0.000778</v>
@@ -49534,10 +49552,8 @@
       <c r="J408" s="5" t="n">
         <v>-0.059413</v>
       </c>
-      <c r="K408" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K408" s="5" t="n">
+        <v>-0.151996</v>
       </c>
       <c r="L408" t="inlineStr">
         <is>
@@ -49603,10 +49619,14 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Gain on mineral property option payments</t>
-        </is>
-      </c>
-      <c r="D409" t="inlineStr"/>
+          <t>Write-down (recovery) of exploration and evaluation assets</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E409" t="inlineStr">
         <is>
           <t>-</t>
@@ -49627,16 +49647,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I409" s="5" t="n">
-        <v>-0.07299899999999999</v>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J409" s="5" t="n">
         <v>-0.025</v>
       </c>
-      <c r="K409" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K409" s="5" t="n">
+        <v>0.068025</v>
       </c>
       <c r="L409" t="inlineStr">
         <is>
@@ -49734,10 +49754,8 @@
       <c r="J410" s="5" t="n">
         <v>0.000348</v>
       </c>
-      <c r="K410" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K410" s="5" t="n">
+        <v>-9.3e-05</v>
       </c>
       <c r="L410" t="inlineStr">
         <is>
@@ -49798,19 +49816,15 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Investing Activity</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Exploration and evaluation assets</t>
-        </is>
-      </c>
-      <c r="D411" t="inlineStr">
-        <is>
-          <t>NetOtherInvestingChanges</t>
-        </is>
-      </c>
+          <t>Option payment received</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr"/>
       <c r="E411" t="inlineStr">
         <is>
           <t>-</t>
@@ -49826,14 +49840,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H411" s="5" t="n">
-        <v>-0.021</v>
-      </c>
-      <c r="I411" s="5" t="n">
-        <v>-0.021526</v>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J411" s="5" t="n">
-        <v>-0.025499</v>
+        <v>0.025</v>
       </c>
       <c r="K411" t="inlineStr">
         <is>
@@ -49899,12 +49917,12 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Investing Activity</t>
+          <t>Due to related parties                                                   65,500     ―</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Option payment received</t>
+          <t>Net cash provided (Used) During the Year</t>
         </is>
       </c>
       <c r="D412" t="inlineStr"/>
@@ -49928,16 +49946,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I412" s="5" t="n">
-        <v>0.075</v>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J412" s="5" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="K412" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.069857</v>
+      </c>
+      <c r="K412" s="5" t="n">
+        <v>0.000525</v>
       </c>
       <c r="L412" t="inlineStr">
         <is>
@@ -49998,39 +50016,49 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Investing Activity</t>
+          <t>Due to related parties                                                   65,500     ―</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Reclamation bond</t>
-        </is>
-      </c>
-      <c r="D413" t="inlineStr"/>
-      <c r="E413" s="5" t="n">
-        <v>-6.600000000000001e-05</v>
-      </c>
-      <c r="F413" s="5" t="n">
-        <v>-0.000114</v>
-      </c>
-      <c r="G413" s="5" t="n">
-        <v>-6.999999999999999e-05</v>
+          <t>Cash – Beginning of Year</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H413" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I413" s="5" t="n">
-        <v>-0.000132</v>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J413" s="5" t="n">
-        <v>-2.9e-05</v>
-      </c>
-      <c r="K413" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.072965</v>
+      </c>
+      <c r="K413" s="5" t="n">
+        <v>0.003108</v>
       </c>
       <c r="L413" t="inlineStr">
         <is>
@@ -50091,41 +50119,49 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Investing Activity</t>
+          <t>Due to related parties                                                   65,500     ―</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Investing Activity total</t>
+          <t>Cash – End of Year $</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
-      <c r="E414" s="5" t="n">
-        <v>-0.02109</v>
-      </c>
-      <c r="F414" s="5" t="n">
-        <v>-0.042114</v>
-      </c>
-      <c r="G414" s="5" t="n">
-        <v>-0.002071</v>
-      </c>
-      <c r="H414" s="5" t="n">
-        <v>-0.021</v>
-      </c>
-      <c r="I414" s="5" t="n">
-        <v>0.053342</v>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J414" s="5" t="n">
-        <v>-0.000528</v>
-      </c>
-      <c r="K414" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.003108</v>
+      </c>
+      <c r="K414" s="5" t="n">
+        <v>0.003633</v>
       </c>
       <c r="L414" t="inlineStr">
         <is>
@@ -50186,12 +50222,12 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>―        81,002</t>
+          <t>Supplementary cash flow information: (See Note 14)</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Net cash provided (Used) During the Year</t>
+          <t>Interest paid in cash $</t>
         </is>
       </c>
       <c r="D415" t="inlineStr"/>
@@ -50215,11 +50251,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I415" s="5" t="n">
-        <v>0.053509</v>
-      </c>
-      <c r="J415" s="5" t="n">
-        <v>-0.069857</v>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K415" t="inlineStr">
         <is>
@@ -50285,19 +50325,15 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>―        81,002</t>
+          <t>Supplementary cash flow information: (See Note 14)</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Cash– Beginning of Year</t>
-        </is>
-      </c>
-      <c r="D416" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Income taxes paid in cash $</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr"/>
       <c r="E416" t="inlineStr">
         <is>
           <t>-</t>
@@ -50318,11 +50354,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I416" s="5" t="n">
-        <v>0.019456</v>
-      </c>
-      <c r="J416" s="5" t="n">
-        <v>0.072965</v>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K416" t="inlineStr">
         <is>
@@ -50388,19 +50428,15 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>―        81,002</t>
+          <t>Adjustments for items not involving cash</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Cash – End of Year $</t>
-        </is>
-      </c>
-      <c r="D417" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
+          <t>Gain on mineral property option payments</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr">
         <is>
           <t>-</t>
@@ -50422,10 +50458,10 @@
         </is>
       </c>
       <c r="I417" s="5" t="n">
-        <v>0.072965</v>
+        <v>-0.07299899999999999</v>
       </c>
       <c r="J417" s="5" t="n">
-        <v>0.003108</v>
+        <v>-0.025</v>
       </c>
       <c r="K417" t="inlineStr">
         <is>
@@ -50491,15 +50527,19 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Supplementary cash flow information: (See Note 14)</t>
+          <t>Investing Activity</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Interest paid in cash $</t>
-        </is>
-      </c>
-      <c r="D418" t="inlineStr"/>
+          <t>Exploration and evaluation assets</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E418" t="inlineStr">
         <is>
           <t>-</t>
@@ -50515,20 +50555,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H418" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I418" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J418" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H418" s="5" t="n">
+        <v>-0.021</v>
+      </c>
+      <c r="I418" s="5" t="n">
+        <v>-0.021526</v>
+      </c>
+      <c r="J418" s="5" t="n">
+        <v>-0.025499</v>
       </c>
       <c r="K418" t="inlineStr">
         <is>
@@ -50594,12 +50628,12 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Supplementary cash flow information: (See Note 14)</t>
+          <t>Investing Activity</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Income taxes paid in cash $</t>
+          <t>Option payment received</t>
         </is>
       </c>
       <c r="D419" t="inlineStr"/>
@@ -50623,15 +50657,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I419" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J419" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I419" s="5" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="J419" s="5" t="n">
+        <v>0.025</v>
       </c>
       <c r="K419" t="inlineStr">
         <is>
@@ -50697,29 +50727,23 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>(70,796)      (20,479)      (91,275)      (59,413)       (150,688)                              Total</t>
+          <t>Investing Activity</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Deficit (5,819,421) (20,479) (59,413)</t>
+          <t>Reclamation bond</t>
         </is>
       </c>
       <c r="D420" t="inlineStr"/>
-      <c r="E420" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F420" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G420" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E420" s="5" t="n">
+        <v>-6.600000000000001e-05</v>
+      </c>
+      <c r="F420" s="5" t="n">
+        <v>-0.000114</v>
+      </c>
+      <c r="G420" s="5" t="n">
+        <v>-6.999999999999999e-05</v>
       </c>
       <c r="H420" t="inlineStr">
         <is>
@@ -50727,10 +50751,10 @@
         </is>
       </c>
       <c r="I420" s="5" t="n">
-        <v>-5.8399</v>
+        <v>-0.000132</v>
       </c>
       <c r="J420" s="5" t="n">
-        <v>-5.899313</v>
+        <v>-2.9e-05</v>
       </c>
       <c r="K420" t="inlineStr">
         <is>
@@ -50796,40 +50820,36 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>(70,796)      (20,479)      (91,275)      (59,413)       (150,688)                              Total</t>
+          <t>Investing Activity</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>― 447,156 ― Reserves</t>
-        </is>
-      </c>
-      <c r="D421" t="inlineStr"/>
-      <c r="E421" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F421" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G421" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H421" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Investing Activity total</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E421" s="5" t="n">
+        <v>-0.02109</v>
+      </c>
+      <c r="F421" s="5" t="n">
+        <v>-0.042114</v>
+      </c>
+      <c r="G421" s="5" t="n">
+        <v>-0.002071</v>
+      </c>
+      <c r="H421" s="5" t="n">
+        <v>-0.021</v>
       </c>
       <c r="I421" s="5" t="n">
-        <v>0.447156</v>
+        <v>0.053342</v>
       </c>
       <c r="J421" s="5" t="n">
-        <v>0.447156</v>
+        <v>-0.000528</v>
       </c>
       <c r="K421" t="inlineStr">
         <is>
@@ -50895,12 +50915,12 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>5,301,469 ―         5,301,469 ―                                    Amount        $                                                           $5,301,469                               Capital</t>
+          <t>―        81,002</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>5,301,469 ―         5,301,469 ―                                    Amount        $                                                           $5,301,469                               Capital of ― ― Share DEFICIENCY NumberShares 16,047,239</t>
+          <t>Net cash provided (Used) During the Year</t>
         </is>
       </c>
       <c r="D422" t="inlineStr"/>
@@ -50925,10 +50945,10 @@
         </is>
       </c>
       <c r="I422" s="5" t="n">
-        <v>16.047239</v>
+        <v>0.053509</v>
       </c>
       <c r="J422" s="5" t="n">
-        <v>16.047239</v>
+        <v>-0.069857</v>
       </c>
       <c r="K422" t="inlineStr">
         <is>
@@ -50994,15 +51014,19 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>to                      Dollars)</t>
+          <t>―        81,002</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>October 2011 2012 2013 notes CHANGES 31,</t>
-        </is>
-      </c>
-      <c r="D423" t="inlineStr"/>
+          <t>Cash– Beginning of Year</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E423" t="inlineStr">
         <is>
           <t>-</t>
@@ -51024,10 +51048,10 @@
         </is>
       </c>
       <c r="I423" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>0.019456</v>
       </c>
       <c r="J423" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>0.072965</v>
       </c>
       <c r="K423" t="inlineStr">
         <is>
@@ -51093,15 +51117,19 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Adjustments for items not involving cash</t>
+          <t>―        81,002</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Write down of mineral properties</t>
-        </is>
-      </c>
-      <c r="D424" t="inlineStr"/>
+          <t>Cash – End of Year $</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E424" t="inlineStr">
         <is>
           <t>-</t>
@@ -51117,18 +51145,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H424" s="5" t="n">
-        <v>0.606119</v>
-      </c>
-      <c r="I424" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J424" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I424" s="5" t="n">
+        <v>0.072965</v>
+      </c>
+      <c r="J424" s="5" t="n">
+        <v>0.003108</v>
       </c>
       <c r="K424" t="inlineStr">
         <is>
@@ -51194,12 +51220,12 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Adjustments for items not involving cash</t>
+          <t>(70,796)      (20,479)      (91,275)      (59,413)       (150,688)                              Total</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Net mineral property option revenue</t>
+          <t>Deficit (5,819,421) (20,479) (59,413)</t>
         </is>
       </c>
       <c r="D425" t="inlineStr"/>
@@ -51224,12 +51250,10 @@
         </is>
       </c>
       <c r="I425" s="5" t="n">
-        <v>-0.07299899999999999</v>
-      </c>
-      <c r="J425" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-5.8399</v>
+      </c>
+      <c r="J425" s="5" t="n">
+        <v>-5.899313</v>
       </c>
       <c r="K425" t="inlineStr">
         <is>
@@ -51295,34 +51319,40 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Financing Activity</t>
+          <t>(70,796)      (20,479)      (91,275)      (59,413)       (150,688)                              Total</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Due to related parties</t>
+          <t>― 447,156 ― Reserves</t>
         </is>
       </c>
       <c r="D426" t="inlineStr"/>
-      <c r="E426" s="5" t="n">
-        <v>-0.0005</v>
-      </c>
-      <c r="F426" s="5" t="n">
-        <v>0.0003</v>
-      </c>
-      <c r="G426" s="5" t="n">
-        <v>0.004469</v>
-      </c>
-      <c r="H426" s="5" t="n">
-        <v>0.101279</v>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I426" s="5" t="n">
-        <v>0.09714299999999999</v>
-      </c>
-      <c r="J426" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.447156</v>
+      </c>
+      <c r="J426" s="5" t="n">
+        <v>0.447156</v>
       </c>
       <c r="K426" t="inlineStr">
         <is>
@@ -51388,38 +51418,40 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Financing Activity</t>
+          <t>5,301,469 ―         5,301,469 ―                                    Amount        $                                                           $5,301,469                               Capital</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Financing Activity total</t>
-        </is>
-      </c>
-      <c r="D427" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
-      <c r="E427" s="5" t="n">
-        <v>0.162</v>
-      </c>
-      <c r="F427" s="5" t="n">
-        <v>0.0003</v>
-      </c>
-      <c r="G427" s="5" t="n">
-        <v>0.044469</v>
-      </c>
-      <c r="H427" s="5" t="n">
-        <v>0.101279</v>
+          <t>5,301,469 ―         5,301,469 ―                                    Amount        $                                                           $5,301,469                               Capital of ― ― Share DEFICIENCY NumberShares 16,047,239</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr"/>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I427" s="5" t="n">
-        <v>0.09714299999999999</v>
-      </c>
-      <c r="J427" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>16.047239</v>
+      </c>
+      <c r="J427" s="5" t="n">
+        <v>16.047239</v>
       </c>
       <c r="K427" t="inlineStr">
         <is>
@@ -51485,34 +51517,40 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Financing Activity</t>
+          <t>to                      Dollars)</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Net Cash and cash equivalents Provided (Used) During the Year</t>
+          <t>October 2011 2012 2013 notes CHANGES 31,</t>
         </is>
       </c>
       <c r="D428" t="inlineStr"/>
-      <c r="E428" s="5" t="n">
-        <v>0.07738299999999999</v>
-      </c>
-      <c r="F428" s="5" t="n">
-        <v>-0.076156</v>
-      </c>
-      <c r="G428" s="5" t="n">
-        <v>-0.046424</v>
-      </c>
-      <c r="H428" s="5" t="n">
-        <v>-0.005181</v>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I428" s="5" t="n">
-        <v>0.053509</v>
-      </c>
-      <c r="J428" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.1e-05</v>
+      </c>
+      <c r="J428" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="K428" t="inlineStr">
         <is>
@@ -51578,33 +51616,37 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Financing Activity</t>
+          <t>Adjustments for items not involving cash</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents – Beginning of Year</t>
-        </is>
-      </c>
-      <c r="D429" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
-      <c r="E429" s="5" t="n">
-        <v>0.06983399999999999</v>
-      </c>
-      <c r="F429" s="5" t="n">
-        <v>0.147217</v>
-      </c>
-      <c r="G429" s="5" t="n">
-        <v>0.071061</v>
+          <t>Write down of mineral properties</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr"/>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H429" s="5" t="n">
-        <v>0.024637</v>
-      </c>
-      <c r="I429" s="5" t="n">
-        <v>0.019456</v>
+        <v>0.606119</v>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J429" t="inlineStr">
         <is>
@@ -51675,33 +51717,37 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Financing Activity</t>
+          <t>Adjustments for items not involving cash</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents – End of Year $</t>
-        </is>
-      </c>
-      <c r="D430" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
-      <c r="E430" s="5" t="n">
-        <v>0.147217</v>
-      </c>
-      <c r="F430" s="5" t="n">
-        <v>0.071061</v>
-      </c>
-      <c r="G430" s="5" t="n">
-        <v>0.024637</v>
-      </c>
-      <c r="H430" s="5" t="n">
-        <v>0.019456</v>
+          <t>Net mineral property option revenue</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr"/>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I430" s="5" t="n">
-        <v>0.072965</v>
+        <v>-0.07299899999999999</v>
       </c>
       <c r="J430" t="inlineStr">
         <is>
@@ -51772,31 +51818,29 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Adjustments for items not involving cash</t>
+          <t>Financing Activity</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Imputed interest</t>
+          <t>Due to related parties</t>
         </is>
       </c>
       <c r="D431" t="inlineStr"/>
       <c r="E431" s="5" t="n">
-        <v>0.005398</v>
+        <v>-0.0005</v>
       </c>
       <c r="F431" s="5" t="n">
-        <v>0.002307</v>
+        <v>0.0003</v>
       </c>
       <c r="G431" s="5" t="n">
-        <v>0.001024</v>
+        <v>0.004469</v>
       </c>
       <c r="H431" s="5" t="n">
-        <v>0.002172</v>
-      </c>
-      <c r="I431" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.101279</v>
+      </c>
+      <c r="I431" s="5" t="n">
+        <v>0.09714299999999999</v>
       </c>
       <c r="J431" t="inlineStr">
         <is>
@@ -51867,35 +51911,33 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital components</t>
+          <t>Financing Activity</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Sales taxes receivable</t>
-        </is>
-      </c>
-      <c r="D432" t="inlineStr"/>
-      <c r="E432" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F432" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Financing Activity total</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E432" s="5" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="F432" s="5" t="n">
+        <v>0.0003</v>
       </c>
       <c r="G432" s="5" t="n">
-        <v>-0.001346</v>
+        <v>0.044469</v>
       </c>
       <c r="H432" s="5" t="n">
-        <v>-0.000105</v>
-      </c>
-      <c r="I432" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.101279</v>
+      </c>
+      <c r="I432" s="5" t="n">
+        <v>0.09714299999999999</v>
       </c>
       <c r="J432" t="inlineStr">
         <is>
@@ -51966,35 +52008,29 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Reclamation bond                           ―            (70)</t>
+          <t>Financing Activity</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Mineral property acquisitions and exploration</t>
+          <t>Net Cash and cash equivalents Provided (Used) During the Year</t>
         </is>
       </c>
       <c r="D433" t="inlineStr"/>
-      <c r="E433" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F433" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E433" s="5" t="n">
+        <v>0.07738299999999999</v>
+      </c>
+      <c r="F433" s="5" t="n">
+        <v>-0.076156</v>
       </c>
       <c r="G433" s="5" t="n">
-        <v>-0.002001</v>
+        <v>-0.046424</v>
       </c>
       <c r="H433" s="5" t="n">
-        <v>-0.021</v>
-      </c>
-      <c r="I433" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.005181</v>
+      </c>
+      <c r="I433" s="5" t="n">
+        <v>0.053509</v>
       </c>
       <c r="J433" t="inlineStr">
         <is>
@@ -52065,35 +52101,33 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Reclamation bond                           ―            (70)</t>
+          <t>Financing Activity</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Reclamation bond                           ―            (70) total</t>
-        </is>
-      </c>
-      <c r="D434" t="inlineStr"/>
-      <c r="E434" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F434" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash and cash equivalents – Beginning of Year</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E434" s="5" t="n">
+        <v>0.06983399999999999</v>
+      </c>
+      <c r="F434" s="5" t="n">
+        <v>0.147217</v>
       </c>
       <c r="G434" s="5" t="n">
-        <v>-0.002071</v>
+        <v>0.071061</v>
       </c>
       <c r="H434" s="5" t="n">
-        <v>-0.021</v>
-      </c>
-      <c r="I434" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.024637</v>
+      </c>
+      <c r="I434" s="5" t="n">
+        <v>0.019456</v>
       </c>
       <c r="J434" t="inlineStr">
         <is>
@@ -52164,35 +52198,33 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Cash advanced by a related party                     ―        40,000</t>
+          <t>Financing Activity</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Due to related parties</t>
-        </is>
-      </c>
-      <c r="D435" t="inlineStr"/>
-      <c r="E435" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F435" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash and cash equivalents – End of Year $</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E435" s="5" t="n">
+        <v>0.147217</v>
+      </c>
+      <c r="F435" s="5" t="n">
+        <v>0.071061</v>
       </c>
       <c r="G435" s="5" t="n">
-        <v>0.004469</v>
+        <v>0.024637</v>
       </c>
       <c r="H435" s="5" t="n">
-        <v>0.098875</v>
-      </c>
-      <c r="I435" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.019456</v>
+      </c>
+      <c r="I435" s="5" t="n">
+        <v>0.072965</v>
       </c>
       <c r="J435" t="inlineStr">
         <is>
@@ -52263,30 +52295,26 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Cash advanced by a related party                     ―        40,000</t>
+          <t>Adjustments for items not involving cash</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Cash advanced by a related party                     ―        40,000 total</t>
+          <t>Imputed interest</t>
         </is>
       </c>
       <c r="D436" t="inlineStr"/>
-      <c r="E436" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F436" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E436" s="5" t="n">
+        <v>0.005398</v>
+      </c>
+      <c r="F436" s="5" t="n">
+        <v>0.002307</v>
       </c>
       <c r="G436" s="5" t="n">
-        <v>0.044469</v>
+        <v>0.001024</v>
       </c>
       <c r="H436" s="5" t="n">
-        <v>0.098875</v>
+        <v>0.002172</v>
       </c>
       <c r="I436" t="inlineStr">
         <is>
@@ -52362,12 +52390,12 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Cash advanced by a related party                     ―        40,000</t>
+          <t>Net changes in non-cash working capital components</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Net Cash and cash equivalents Provided (Used) During the Year</t>
+          <t>Sales taxes receivable</t>
         </is>
       </c>
       <c r="D437" t="inlineStr"/>
@@ -52382,10 +52410,10 @@
         </is>
       </c>
       <c r="G437" s="5" t="n">
-        <v>-0.046424</v>
+        <v>-0.001346</v>
       </c>
       <c r="H437" s="5" t="n">
-        <v>-0.005181</v>
+        <v>-0.000105</v>
       </c>
       <c r="I437" t="inlineStr">
         <is>
@@ -52461,19 +52489,15 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Cash advanced by a related party                     ―        40,000</t>
+          <t>Reclamation bond                           ―            (70)</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents – Beginning of Year</t>
-        </is>
-      </c>
-      <c r="D438" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Mineral property acquisitions and exploration</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr"/>
       <c r="E438" t="inlineStr">
         <is>
           <t>-</t>
@@ -52485,10 +52509,10 @@
         </is>
       </c>
       <c r="G438" s="5" t="n">
-        <v>0.071061</v>
+        <v>-0.002001</v>
       </c>
       <c r="H438" s="5" t="n">
-        <v>0.024637</v>
+        <v>-0.021</v>
       </c>
       <c r="I438" t="inlineStr">
         <is>
@@ -52564,19 +52588,15 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Cash advanced by a related party                     ―        40,000</t>
+          <t>Reclamation bond                           ―            (70)</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents – End of Year $</t>
-        </is>
-      </c>
-      <c r="D439" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
+          <t>Reclamation bond                           ―            (70) total</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr"/>
       <c r="E439" t="inlineStr">
         <is>
           <t>-</t>
@@ -52588,10 +52608,10 @@
         </is>
       </c>
       <c r="G439" s="5" t="n">
-        <v>0.024637</v>
+        <v>-0.002071</v>
       </c>
       <c r="H439" s="5" t="n">
-        <v>0.019456</v>
+        <v>-0.021</v>
       </c>
       <c r="I439" t="inlineStr">
         <is>
@@ -52667,12 +52687,12 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Supplementary cash flow information: (See Note 11)</t>
+          <t>Cash advanced by a related party                     ―        40,000</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Interest paid in cash $</t>
+          <t>Due to related parties</t>
         </is>
       </c>
       <c r="D440" t="inlineStr"/>
@@ -52686,15 +52706,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G440" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H440" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G440" s="5" t="n">
+        <v>0.004469</v>
+      </c>
+      <c r="H440" s="5" t="n">
+        <v>0.098875</v>
       </c>
       <c r="I440" t="inlineStr">
         <is>
@@ -52770,12 +52786,12 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Supplementary cash flow information: (See Note 11)</t>
+          <t>Cash advanced by a related party                     ―        40,000</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Income taxes paid in cash $</t>
+          <t>Cash advanced by a related party                     ―        40,000 total</t>
         </is>
       </c>
       <c r="D441" t="inlineStr"/>
@@ -52789,15 +52805,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G441" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H441" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G441" s="5" t="n">
+        <v>0.044469</v>
+      </c>
+      <c r="H441" s="5" t="n">
+        <v>0.098875</v>
       </c>
       <c r="I441" t="inlineStr">
         <is>
@@ -52873,12 +52885,12 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Adjustments for items not involving cash</t>
+          <t>Cash advanced by a related party                     ―        40,000</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Director’s fee settled by shares</t>
+          <t>Net Cash and cash equivalents Provided (Used) During the Year</t>
         </is>
       </c>
       <c r="D442" t="inlineStr"/>
@@ -52887,18 +52899,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F442" s="5" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="G442" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H442" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G442" s="5" t="n">
+        <v>-0.046424</v>
+      </c>
+      <c r="H442" s="5" t="n">
+        <v>-0.005181</v>
       </c>
       <c r="I442" t="inlineStr">
         <is>
@@ -52974,15 +52984,19 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Adjustments for items not involving cash</t>
+          <t>Cash advanced by a related party                     ―        40,000</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Administration (office rent) settled by shares</t>
-        </is>
-      </c>
-      <c r="D443" t="inlineStr"/>
+          <t>Cash and cash equivalents – Beginning of Year</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E443" t="inlineStr">
         <is>
           <t>-</t>
@@ -52994,12 +53008,10 @@
         </is>
       </c>
       <c r="G443" s="5" t="n">
-        <v>0.010426</v>
-      </c>
-      <c r="H443" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.071061</v>
+      </c>
+      <c r="H443" s="5" t="n">
+        <v>0.024637</v>
       </c>
       <c r="I443" t="inlineStr">
         <is>
@@ -53075,21 +53087,23 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Adjustments for items not involving cash</t>
+          <t>Cash advanced by a related party                     ―        40,000</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Stock based compensation</t>
+          <t>Cash and cash equivalents – End of Year $</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
-      <c r="E444" s="5" t="n">
-        <v>0.373182</v>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -53097,12 +53111,10 @@
         </is>
       </c>
       <c r="G444" s="5" t="n">
-        <v>0.044307</v>
-      </c>
-      <c r="H444" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.024637</v>
+      </c>
+      <c r="H444" s="5" t="n">
+        <v>0.019456</v>
       </c>
       <c r="I444" t="inlineStr">
         <is>
@@ -53178,27 +53190,29 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital components</t>
+          <t>Supplementary cash flow information: (See Note 11)</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Other receivable</t>
-        </is>
-      </c>
-      <c r="D445" t="inlineStr">
-        <is>
-          <t>ChangeInReceivables</t>
-        </is>
-      </c>
-      <c r="E445" s="5" t="n">
-        <v>9.500000000000001e-05</v>
-      </c>
-      <c r="F445" s="5" t="n">
-        <v>0.000494</v>
-      </c>
-      <c r="G445" s="5" t="n">
-        <v>-0.001346</v>
+          <t>Interest paid in cash $</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr"/>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H445" t="inlineStr">
         <is>
@@ -53279,23 +53293,29 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Investing Activity</t>
+          <t>Supplementary cash flow information: (See Note 11)</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Mineral property acquisitions and exploration</t>
+          <t>Income taxes paid in cash $</t>
         </is>
       </c>
       <c r="D446" t="inlineStr"/>
-      <c r="E446" s="5" t="n">
-        <v>-0.021024</v>
-      </c>
-      <c r="F446" s="5" t="n">
-        <v>-0.042</v>
-      </c>
-      <c r="G446" s="5" t="n">
-        <v>-0.002001</v>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H446" t="inlineStr">
         <is>
@@ -53376,12 +53396,12 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Financing Activity</t>
+          <t>Adjustments for items not involving cash</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Cash advanced by a related party</t>
+          <t>Director’s fee settled by shares</t>
         </is>
       </c>
       <c r="D447" t="inlineStr"/>
@@ -53390,13 +53410,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F447" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G447" s="5" t="n">
-        <v>0.04</v>
+      <c r="F447" s="5" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H447" t="inlineStr">
         <is>
@@ -53477,27 +53497,27 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Financing Activity</t>
+          <t>Adjustments for items not involving cash</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Shares issued for cash</t>
+          <t>Administration (office rent) settled by shares</t>
         </is>
       </c>
       <c r="D448" t="inlineStr"/>
-      <c r="E448" s="5" t="n">
-        <v>0.1625</v>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F448" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G448" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G448" s="5" t="n">
+        <v>0.010426</v>
       </c>
       <c r="H448" t="inlineStr">
         <is>
@@ -53578,29 +53598,29 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Supplementary cash flow information:(See Note 11)</t>
+          <t>Adjustments for items not involving cash</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Interest paid in cash $</t>
-        </is>
-      </c>
-      <c r="D449" t="inlineStr"/>
-      <c r="E449" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Stock based compensation</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E449" s="5" t="n">
+        <v>0.373182</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G449" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G449" s="5" t="n">
+        <v>0.044307</v>
       </c>
       <c r="H449" t="inlineStr">
         <is>
@@ -53681,29 +53701,27 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Supplementary cash flow information:(See Note 11)</t>
+          <t>Net changes in non-cash working capital components</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Income taxes paid in cash $</t>
-        </is>
-      </c>
-      <c r="D450" t="inlineStr"/>
-      <c r="E450" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F450" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G450" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Other receivable</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E450" s="5" t="n">
+        <v>9.500000000000001e-05</v>
+      </c>
+      <c r="F450" s="5" t="n">
+        <v>0.000494</v>
+      </c>
+      <c r="G450" s="5" t="n">
+        <v>-0.001346</v>
       </c>
       <c r="H450" t="inlineStr">
         <is>
@@ -53779,38 +53797,28 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Investing Activity</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Depreciation 5</t>
-        </is>
-      </c>
-      <c r="D451" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="E451" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F451" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G451" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Mineral property acquisitions and exploration</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr"/>
+      <c r="E451" s="5" t="n">
+        <v>-0.021024</v>
+      </c>
+      <c r="F451" s="5" t="n">
+        <v>-0.042</v>
+      </c>
+      <c r="G451" s="5" t="n">
+        <v>-0.002001</v>
       </c>
       <c r="H451" t="inlineStr">
         <is>
@@ -53872,27 +53880,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="T451" s="5" t="n">
-        <v>0.037106</v>
-      </c>
-      <c r="U451" s="5" t="n">
-        <v>0.009686</v>
+      <c r="T451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Financing Activity</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenses 6</t>
+          <t>Cash advanced by a related party</t>
         </is>
       </c>
       <c r="D452" t="inlineStr"/>
@@ -53906,10 +53918,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G452" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G452" s="5" t="n">
+        <v>0.04</v>
       </c>
       <c r="H452" t="inlineStr">
         <is>
@@ -53971,38 +53981,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="T452" s="5" t="n">
-        <v>0.307574</v>
-      </c>
-      <c r="U452" s="5" t="n">
-        <v>1.169229</v>
+      <c r="T452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Financing Activity</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>General and administration</t>
+          <t>Shares issued for cash</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E453" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
+      <c r="E453" s="5" t="n">
+        <v>0.1625</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -54074,27 +54086,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="T453" s="5" t="n">
-        <v>0.153948</v>
-      </c>
-      <c r="U453" s="5" t="n">
-        <v>0.141093</v>
+      <c r="T453" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U453" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Supplementary cash flow information:(See Note 11)</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Management fee and wages 10</t>
+          <t>Interest paid in cash $</t>
         </is>
       </c>
       <c r="D454" t="inlineStr"/>
@@ -54173,34 +54189,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="T454" s="5" t="n">
-        <v>0.201888</v>
-      </c>
-      <c r="U454" s="5" t="n">
-        <v>0.15</v>
+      <c r="T454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Supplementary cash flow information:(See Note 11)</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Marketing and professional fees</t>
-        </is>
-      </c>
-      <c r="D455" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Income taxes paid in cash $</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr"/>
       <c r="E455" t="inlineStr">
         <is>
           <t>-</t>
@@ -54276,11 +54292,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="T455" s="5" t="n">
-        <v>0.275445</v>
-      </c>
-      <c r="U455" s="5" t="n">
-        <v>0.307836</v>
+      <c r="T455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="456">
@@ -54296,10 +54316,14 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Share-based payments, net of forfeitures 9</t>
-        </is>
-      </c>
-      <c r="D456" t="inlineStr"/>
+          <t>Depreciation 5</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E456" t="inlineStr">
         <is>
           <t>-</t>
@@ -54376,10 +54400,10 @@
         </is>
       </c>
       <c r="T456" s="5" t="n">
-        <v>0.120586</v>
+        <v>0.037106</v>
       </c>
       <c r="U456" s="5" t="n">
-        <v>0.018356</v>
+        <v>0.009686</v>
       </c>
     </row>
     <row r="457">
@@ -54395,7 +54419,7 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Tax and penalties</t>
+          <t>Exploration and evaluation expenses 6</t>
         </is>
       </c>
       <c r="D457" t="inlineStr"/>
@@ -54475,12 +54499,10 @@
         </is>
       </c>
       <c r="T457" s="5" t="n">
-        <v>0.370895</v>
-      </c>
-      <c r="U457" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.307574</v>
+      </c>
+      <c r="U457" s="5" t="n">
+        <v>1.169229</v>
       </c>
     </row>
     <row r="458">
@@ -54496,12 +54518,12 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>TOTAL EXPENSES</t>
+          <t>General and administration</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
@@ -54580,10 +54602,10 @@
         </is>
       </c>
       <c r="T458" s="5" t="n">
-        <v>1.467442</v>
+        <v>0.153948</v>
       </c>
       <c r="U458" s="5" t="n">
-        <v>1.7962</v>
+        <v>0.141093</v>
       </c>
     </row>
     <row r="459">
@@ -54594,19 +54616,15 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Other Items</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Foreign exchange gain (loss)</t>
-        </is>
-      </c>
-      <c r="D459" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Management fee and wages 10</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr"/>
       <c r="E459" t="inlineStr">
         <is>
           <t>-</t>
@@ -54683,10 +54701,10 @@
         </is>
       </c>
       <c r="T459" s="5" t="n">
-        <v>-0.03884</v>
+        <v>0.201888</v>
       </c>
       <c r="U459" s="5" t="n">
-        <v>0.035649</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="460">
@@ -54697,17 +54715,17 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Other Items</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Interest expense 8</t>
+          <t>Marketing and professional fees</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>InterestExpenseOperating</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
@@ -54786,10 +54804,10 @@
         </is>
       </c>
       <c r="T460" s="5" t="n">
-        <v>-0.039371</v>
+        <v>0.275445</v>
       </c>
       <c r="U460" s="5" t="n">
-        <v>-0.048554</v>
+        <v>0.307836</v>
       </c>
     </row>
     <row r="461">
@@ -54800,12 +54818,12 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Other Items</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Write-off of property, plant and equipment</t>
+          <t>Share-based payments, net of forfeitures 9</t>
         </is>
       </c>
       <c r="D461" t="inlineStr"/>
@@ -54885,12 +54903,10 @@
         </is>
       </c>
       <c r="T461" s="5" t="n">
-        <v>-0.002949</v>
-      </c>
-      <c r="U461" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.120586</v>
+      </c>
+      <c r="U461" s="5" t="n">
+        <v>0.018356</v>
       </c>
     </row>
     <row r="462">
@@ -54901,19 +54917,15 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Other Items</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>NET LOSS FOR THE YEAR</t>
-        </is>
-      </c>
-      <c r="D462" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Tax and penalties</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr"/>
       <c r="E462" t="inlineStr">
         <is>
           <t>-</t>
@@ -54990,10 +55002,12 @@
         </is>
       </c>
       <c r="T462" s="5" t="n">
-        <v>-1.548602</v>
-      </c>
-      <c r="U462" s="5" t="n">
-        <v>-1.809105</v>
+        <v>0.370895</v>
+      </c>
+      <c r="U462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="463">
@@ -55004,15 +55018,19 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Foreign currency translation differences for foreign</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Foreign currency translation differences for foreign operations</t>
-        </is>
-      </c>
-      <c r="D463" t="inlineStr"/>
+          <t>TOTAL EXPENSES</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E463" t="inlineStr">
         <is>
           <t>-</t>
@@ -55089,10 +55107,10 @@
         </is>
       </c>
       <c r="T463" s="5" t="n">
-        <v>0.142739</v>
+        <v>1.467442</v>
       </c>
       <c r="U463" s="5" t="n">
-        <v>-0.110922</v>
+        <v>1.7962</v>
       </c>
     </row>
     <row r="464">
@@ -55103,17 +55121,17 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Foreign currency translation differences for foreign</t>
+          <t>Other Items</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>COMPREHENSIVE LOSS FOR THE YEAR</t>
+          <t>Foreign exchange gain (loss)</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
@@ -55192,10 +55210,10 @@
         </is>
       </c>
       <c r="T464" s="5" t="n">
-        <v>-1.405863</v>
+        <v>-0.03884</v>
       </c>
       <c r="U464" s="5" t="n">
-        <v>-1.920027</v>
+        <v>0.035649</v>
       </c>
     </row>
     <row r="465">
@@ -55206,15 +55224,19 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Foreign currency translation differences for foreign</t>
+          <t>Other Items</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share for the year</t>
-        </is>
-      </c>
-      <c r="D465" t="inlineStr"/>
+          <t>Interest expense 8</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
       <c r="E465" t="inlineStr">
         <is>
           <t>-</t>
@@ -55291,10 +55313,10 @@
         </is>
       </c>
       <c r="T465" s="5" t="n">
-        <v>-4e-08</v>
+        <v>-0.039371</v>
       </c>
       <c r="U465" s="5" t="n">
-        <v>-4e-08</v>
+        <v>-0.048554</v>
       </c>
     </row>
     <row r="466">
@@ -55305,12 +55327,12 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>Other Items</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding, basic and diluted</t>
+          <t>Write-off of property, plant and equipment</t>
         </is>
       </c>
       <c r="D466" t="inlineStr"/>
@@ -55384,14 +55406,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S466" s="5" t="n">
-        <v>201.826357</v>
+      <c r="S466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="T466" s="5" t="n">
-        <v>40.452157</v>
-      </c>
-      <c r="U466" s="5" t="n">
-        <v>42.308802</v>
+        <v>-0.002949</v>
+      </c>
+      <c r="U466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="467">
@@ -55400,13 +55426,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B467" t="inlineStr"/>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>Other Items</t>
+        </is>
+      </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>December 31, 2024 December</t>
-        </is>
-      </c>
-      <c r="D467" t="inlineStr"/>
+          <t>NET LOSS FOR THE YEAR</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E467" t="inlineStr">
         <is>
           <t>-</t>
@@ -55477,16 +55511,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S467" s="5" t="n">
-        <v>0.002023</v>
+      <c r="S467" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="T467" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="U467" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.548602</v>
+      </c>
+      <c r="U467" s="5" t="n">
+        <v>-1.809105</v>
       </c>
     </row>
     <row r="468">
@@ -55497,19 +55531,15 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Foreign currency translation differences for foreign</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Depreciation 6</t>
-        </is>
-      </c>
-      <c r="D468" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>Foreign currency translation differences for foreign operations</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr"/>
       <c r="E468" t="inlineStr">
         <is>
           <t>-</t>
@@ -55580,16 +55610,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S468" s="5" t="n">
-        <v>0.105035</v>
+      <c r="S468" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="T468" s="5" t="n">
-        <v>0.037106</v>
-      </c>
-      <c r="U468" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.142739</v>
+      </c>
+      <c r="U468" s="5" t="n">
+        <v>-0.110922</v>
       </c>
     </row>
     <row r="469">
@@ -55600,15 +55630,19 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Foreign currency translation differences for foreign</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenses 7</t>
-        </is>
-      </c>
-      <c r="D469" t="inlineStr"/>
+          <t>COMPREHENSIVE LOSS FOR THE YEAR</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E469" t="inlineStr">
         <is>
           <t>-</t>
@@ -55679,16 +55713,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S469" s="5" t="n">
-        <v>0.477592</v>
+      <c r="S469" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="T469" s="5" t="n">
-        <v>0.307574</v>
-      </c>
-      <c r="U469" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.405863</v>
+      </c>
+      <c r="U469" s="5" t="n">
+        <v>-1.920027</v>
       </c>
     </row>
     <row r="470">
@@ -55699,19 +55733,15 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Foreign currency translation differences for foreign</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>General and administration</t>
-        </is>
-      </c>
-      <c r="D470" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Basic and diluted loss per share for the year</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr"/>
       <c r="E470" t="inlineStr">
         <is>
           <t>-</t>
@@ -55757,14 +55787,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N470" s="5" t="n">
-        <v>0.064026</v>
-      </c>
-      <c r="O470" s="5" t="n">
-        <v>0.15116</v>
-      </c>
-      <c r="P470" s="5" t="n">
-        <v>0.223634</v>
+      <c r="N470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q470" t="inlineStr">
         <is>
@@ -55776,16 +55812,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S470" s="5" t="n">
-        <v>0.179733</v>
+      <c r="S470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="T470" s="5" t="n">
-        <v>0.153948</v>
-      </c>
-      <c r="U470" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-4e-08</v>
+      </c>
+      <c r="U470" s="5" t="n">
+        <v>-4e-08</v>
       </c>
     </row>
     <row r="471">
@@ -55796,12 +55832,12 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Weighted average number of common shares</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Management fee and wages 11</t>
+          <t>Weighted average number of common shares outstanding, basic and diluted</t>
         </is>
       </c>
       <c r="D471" t="inlineStr"/>
@@ -55876,15 +55912,13 @@
         </is>
       </c>
       <c r="S471" s="5" t="n">
-        <v>0.15464</v>
+        <v>201.826357</v>
       </c>
       <c r="T471" s="5" t="n">
-        <v>0.201888</v>
-      </c>
-      <c r="U471" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>40.452157</v>
+      </c>
+      <c r="U471" s="5" t="n">
+        <v>42.308802</v>
       </c>
     </row>
     <row r="472">
@@ -55893,21 +55927,13 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B472" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B472" t="inlineStr"/>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Marketing and professional fees</t>
-        </is>
-      </c>
-      <c r="D472" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>December 31, 2024 December</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr"/>
       <c r="E472" t="inlineStr">
         <is>
           <t>-</t>
@@ -55979,10 +56005,10 @@
         </is>
       </c>
       <c r="S472" s="5" t="n">
-        <v>0.446191</v>
+        <v>0.002023</v>
       </c>
       <c r="T472" s="5" t="n">
-        <v>0.275445</v>
+        <v>3.1e-05</v>
       </c>
       <c r="U472" t="inlineStr">
         <is>
@@ -56003,10 +56029,14 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Share-based payments, net of forfeitures 10</t>
-        </is>
-      </c>
-      <c r="D473" t="inlineStr"/>
+          <t>Depreciation 6</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E473" t="inlineStr">
         <is>
           <t>-</t>
@@ -56078,10 +56108,10 @@
         </is>
       </c>
       <c r="S473" s="5" t="n">
-        <v>0.186</v>
+        <v>0.105035</v>
       </c>
       <c r="T473" s="5" t="n">
-        <v>0.120586</v>
+        <v>0.037106</v>
       </c>
       <c r="U473" t="inlineStr">
         <is>
@@ -56102,7 +56132,7 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Tax and penalties</t>
+          <t>Exploration and evaluation expenses 7</t>
         </is>
       </c>
       <c r="D474" t="inlineStr"/>
@@ -56176,13 +56206,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S474" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S474" s="5" t="n">
+        <v>0.477592</v>
       </c>
       <c r="T474" s="5" t="n">
-        <v>0.370895</v>
+        <v>0.307574</v>
       </c>
       <c r="U474" t="inlineStr">
         <is>
@@ -56203,12 +56231,12 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Total expenses</t>
+          <t>General and administration</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
@@ -56256,20 +56284,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N475" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O475" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P475" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N475" s="5" t="n">
+        <v>0.064026</v>
+      </c>
+      <c r="O475" s="5" t="n">
+        <v>0.15116</v>
+      </c>
+      <c r="P475" s="5" t="n">
+        <v>0.223634</v>
       </c>
       <c r="Q475" t="inlineStr">
         <is>
@@ -56282,10 +56304,10 @@
         </is>
       </c>
       <c r="S475" s="5" t="n">
-        <v>1.549191</v>
+        <v>0.179733</v>
       </c>
       <c r="T475" s="5" t="n">
-        <v>1.467442</v>
+        <v>0.153948</v>
       </c>
       <c r="U475" t="inlineStr">
         <is>
@@ -56301,19 +56323,15 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Other Income (expense)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Foreign exchange gain (loss)</t>
-        </is>
-      </c>
-      <c r="D476" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Management fee and wages 11</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr"/>
       <c r="E476" t="inlineStr">
         <is>
           <t>-</t>
@@ -56385,10 +56403,10 @@
         </is>
       </c>
       <c r="S476" s="5" t="n">
-        <v>0.005818</v>
+        <v>0.15464</v>
       </c>
       <c r="T476" s="5" t="n">
-        <v>-0.03884</v>
+        <v>0.201888</v>
       </c>
       <c r="U476" t="inlineStr">
         <is>
@@ -56404,15 +56422,19 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Other Income (expense)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Loss on fixed asset disposal 6</t>
-        </is>
-      </c>
-      <c r="D477" t="inlineStr"/>
+          <t>Marketing and professional fees</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E477" t="inlineStr">
         <is>
           <t>-</t>
@@ -56484,12 +56506,10 @@
         </is>
       </c>
       <c r="S477" s="5" t="n">
-        <v>-0.002774</v>
-      </c>
-      <c r="T477" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.446191</v>
+      </c>
+      <c r="T477" s="5" t="n">
+        <v>0.275445</v>
       </c>
       <c r="U477" t="inlineStr">
         <is>
@@ -56505,19 +56525,15 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Other Income (expense)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Interest and finance income</t>
-        </is>
-      </c>
-      <c r="D478" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Share-based payments, net of forfeitures 10</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr"/>
       <c r="E478" t="inlineStr">
         <is>
           <t>-</t>
@@ -56589,12 +56605,10 @@
         </is>
       </c>
       <c r="S478" s="5" t="n">
-        <v>0.005822</v>
-      </c>
-      <c r="T478" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.186</v>
+      </c>
+      <c r="T478" s="5" t="n">
+        <v>0.120586</v>
       </c>
       <c r="U478" t="inlineStr">
         <is>
@@ -56610,19 +56624,15 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Other Income (expense)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Interest expense 8,9</t>
-        </is>
-      </c>
-      <c r="D479" t="inlineStr">
-        <is>
-          <t>InterestExpenseOperating</t>
-        </is>
-      </c>
+          <t>Tax and penalties</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr"/>
       <c r="E479" t="inlineStr">
         <is>
           <t>-</t>
@@ -56693,11 +56703,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S479" s="5" t="n">
-        <v>-0.024405</v>
+      <c r="S479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="T479" s="5" t="n">
-        <v>-0.039371</v>
+        <v>0.370895</v>
       </c>
       <c r="U479" t="inlineStr">
         <is>
@@ -56713,17 +56725,17 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Write-off of property, plant and equipment                                      (2,949)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Loss for the year</t>
+          <t>Total expenses</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
@@ -56797,10 +56809,10 @@
         </is>
       </c>
       <c r="S480" s="5" t="n">
-        <v>-1.56473</v>
+        <v>1.549191</v>
       </c>
       <c r="T480" s="5" t="n">
-        <v>-1.548602</v>
+        <v>1.467442</v>
       </c>
       <c r="U480" t="inlineStr">
         <is>
@@ -56816,15 +56828,19 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>income (loss)</t>
+          <t>Other Income (expense)</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Cumulative translation adjustment</t>
-        </is>
-      </c>
-      <c r="D481" t="inlineStr"/>
+          <t>Foreign exchange gain (loss)</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E481" t="inlineStr">
         <is>
           <t>-</t>
@@ -56896,10 +56912,10 @@
         </is>
       </c>
       <c r="S481" s="5" t="n">
-        <v>-0.041863</v>
+        <v>0.005818</v>
       </c>
       <c r="T481" s="5" t="n">
-        <v>0.142739</v>
+        <v>-0.03884</v>
       </c>
       <c r="U481" t="inlineStr">
         <is>
@@ -56915,19 +56931,15 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>income (loss)</t>
+          <t>Other Income (expense)</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Comprehensive loss for the year</t>
-        </is>
-      </c>
-      <c r="D482" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Loss on fixed asset disposal 6</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr"/>
       <c r="E482" t="inlineStr">
         <is>
           <t>-</t>
@@ -56999,10 +57011,12 @@
         </is>
       </c>
       <c r="S482" s="5" t="n">
-        <v>-1.606593</v>
-      </c>
-      <c r="T482" s="5" t="n">
-        <v>-1.405863</v>
+        <v>-0.002774</v>
+      </c>
+      <c r="T482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="U482" t="inlineStr">
         <is>
@@ -57018,15 +57032,19 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>income (loss)</t>
+          <t>Other Income (expense)</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share for the year</t>
-        </is>
-      </c>
-      <c r="D483" t="inlineStr"/>
+          <t>Interest and finance income</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E483" t="inlineStr">
         <is>
           <t>-</t>
@@ -57098,10 +57116,12 @@
         </is>
       </c>
       <c r="S483" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="T483" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.005822</v>
+      </c>
+      <c r="T483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="U483" t="inlineStr">
         <is>
@@ -57115,13 +57135,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B484" t="inlineStr"/>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>Other Income (expense)</t>
+        </is>
+      </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>December 31, 2019 December</t>
-        </is>
-      </c>
-      <c r="D484" t="inlineStr"/>
+          <t>Interest expense 8,9</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
       <c r="E484" t="inlineStr">
         <is>
           <t>-</t>
@@ -57172,11 +57200,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O484" s="5" t="n">
-        <v>0.002018</v>
-      </c>
-      <c r="P484" s="5" t="n">
-        <v>3.1e-05</v>
+      <c r="O484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q484" t="inlineStr">
         <is>
@@ -57188,15 +57220,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S484" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T484" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S484" s="5" t="n">
+        <v>-0.024405</v>
+      </c>
+      <c r="T484" s="5" t="n">
+        <v>-0.039371</v>
       </c>
       <c r="U484" t="inlineStr">
         <is>
@@ -57212,15 +57240,19 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Write-off of property, plant and equipment                                      (2,949)</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenses 7 $</t>
-        </is>
-      </c>
-      <c r="D485" t="inlineStr"/>
+          <t>Loss for the year</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E485" t="inlineStr">
         <is>
           <t>-</t>
@@ -57266,14 +57298,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N485" s="5" t="n">
-        <v>0.524152</v>
-      </c>
-      <c r="O485" s="5" t="n">
-        <v>0.875023</v>
-      </c>
-      <c r="P485" s="5" t="n">
-        <v>1.199883</v>
+      <c r="N485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q485" t="inlineStr">
         <is>
@@ -57285,15 +57323,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S485" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T485" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S485" s="5" t="n">
+        <v>-1.56473</v>
+      </c>
+      <c r="T485" s="5" t="n">
+        <v>-1.548602</v>
       </c>
       <c r="U485" t="inlineStr">
         <is>
@@ -57309,12 +57343,12 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>income (loss)</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Management fees, wages and corporate advisory 10</t>
+          <t>Cumulative translation adjustment</t>
         </is>
       </c>
       <c r="D486" t="inlineStr"/>
@@ -57368,11 +57402,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O486" s="5" t="n">
-        <v>0.552042</v>
-      </c>
-      <c r="P486" s="5" t="n">
-        <v>0.64872</v>
+      <c r="O486" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P486" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q486" t="inlineStr">
         <is>
@@ -57384,15 +57422,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S486" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T486" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S486" s="5" t="n">
+        <v>-0.041863</v>
+      </c>
+      <c r="T486" s="5" t="n">
+        <v>0.142739</v>
       </c>
       <c r="U486" t="inlineStr">
         <is>
@@ -57408,17 +57442,17 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>income (loss)</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Marketing, advisory and investor relations</t>
+          <t>Comprehensive loss for the year</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
@@ -57466,14 +57500,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N487" s="5" t="n">
-        <v>0.026221</v>
-      </c>
-      <c r="O487" s="5" t="n">
-        <v>0.238089</v>
-      </c>
-      <c r="P487" s="5" t="n">
-        <v>0.718866</v>
+      <c r="N487" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O487" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P487" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q487" t="inlineStr">
         <is>
@@ -57485,15 +57525,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S487" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T487" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S487" s="5" t="n">
+        <v>-1.606593</v>
+      </c>
+      <c r="T487" s="5" t="n">
+        <v>-1.405863</v>
       </c>
       <c r="U487" t="inlineStr">
         <is>
@@ -57509,19 +57545,15 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>income (loss)</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D488" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Basic and diluted loss per share for the year</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr"/>
       <c r="E488" t="inlineStr">
         <is>
           <t>-</t>
@@ -57567,14 +57599,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N488" s="5" t="n">
-        <v>0.067005</v>
-      </c>
-      <c r="O488" s="5" t="n">
-        <v>0.102527</v>
-      </c>
-      <c r="P488" s="5" t="n">
-        <v>0.579564</v>
+      <c r="N488" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O488" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P488" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q488" t="inlineStr">
         <is>
@@ -57586,15 +57624,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S488" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T488" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S488" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="T488" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="U488" t="inlineStr">
         <is>
@@ -57608,14 +57642,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B489" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B489" t="inlineStr"/>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Share-based payments 9</t>
+          <t>December 31, 2019 December</t>
         </is>
       </c>
       <c r="D489" t="inlineStr"/>
@@ -57670,10 +57700,10 @@
         </is>
       </c>
       <c r="O489" s="5" t="n">
-        <v>0.45325</v>
+        <v>0.002018</v>
       </c>
       <c r="P489" s="5" t="n">
-        <v>0.537207</v>
+        <v>3.1e-05</v>
       </c>
       <c r="Q489" t="inlineStr">
         <is>
@@ -57714,14 +57744,10 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Expenses total</t>
-        </is>
-      </c>
-      <c r="D490" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Exploration and evaluation expenses 7 $</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr"/>
       <c r="E490" t="inlineStr">
         <is>
           <t>-</t>
@@ -57768,13 +57794,13 @@
         </is>
       </c>
       <c r="N490" s="5" t="n">
-        <v>1.188404</v>
+        <v>0.524152</v>
       </c>
       <c r="O490" s="5" t="n">
-        <v>2.372091</v>
+        <v>0.875023</v>
       </c>
       <c r="P490" s="5" t="n">
-        <v>3.907874</v>
+        <v>1.199883</v>
       </c>
       <c r="Q490" t="inlineStr">
         <is>
@@ -57810,19 +57836,15 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Other income/expense</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Foreign exchange gain (loss)</t>
-        </is>
-      </c>
-      <c r="D491" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Management fees, wages and corporate advisory 10</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr"/>
       <c r="E491" t="inlineStr">
         <is>
           <t>-</t>
@@ -57874,10 +57896,10 @@
         </is>
       </c>
       <c r="O491" s="5" t="n">
-        <v>0.009826</v>
+        <v>0.552042</v>
       </c>
       <c r="P491" s="5" t="n">
-        <v>-0.033589</v>
+        <v>0.64872</v>
       </c>
       <c r="Q491" t="inlineStr">
         <is>
@@ -57913,15 +57935,19 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Other income/expense</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Gain on royalty sale 7</t>
-        </is>
-      </c>
-      <c r="D492" t="inlineStr"/>
+          <t>Marketing, advisory and investor relations</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E492" t="inlineStr">
         <is>
           <t>-</t>
@@ -57967,18 +57993,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N492" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O492" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N492" s="5" t="n">
+        <v>0.026221</v>
+      </c>
+      <c r="O492" s="5" t="n">
+        <v>0.238089</v>
       </c>
       <c r="P492" s="5" t="n">
-        <v>2.140749</v>
+        <v>0.718866</v>
       </c>
       <c r="Q492" t="inlineStr">
         <is>
@@ -58014,15 +58036,19 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Other income/expense</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Interest and finance income (expense)</t>
-        </is>
-      </c>
-      <c r="D493" t="inlineStr"/>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E493" t="inlineStr">
         <is>
           <t>-</t>
@@ -58068,16 +58094,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N493" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N493" s="5" t="n">
+        <v>0.067005</v>
       </c>
       <c r="O493" s="5" t="n">
-        <v>-0.001849</v>
+        <v>0.102527</v>
       </c>
       <c r="P493" s="5" t="n">
-        <v>0.01039</v>
+        <v>0.579564</v>
       </c>
       <c r="Q493" t="inlineStr">
         <is>
@@ -58113,12 +58137,12 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Other income/expense</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>Listing expense 5</t>
+          <t>Share-based payments 9</t>
         </is>
       </c>
       <c r="D494" t="inlineStr"/>
@@ -58173,12 +58197,10 @@
         </is>
       </c>
       <c r="O494" s="5" t="n">
-        <v>-2.136955</v>
-      </c>
-      <c r="P494" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.45325</v>
+      </c>
+      <c r="P494" s="5" t="n">
+        <v>0.537207</v>
       </c>
       <c r="Q494" t="inlineStr">
         <is>
@@ -58214,17 +58236,17 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Other income/expense</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Expenses total</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
@@ -58273,15 +58295,13 @@
         </is>
       </c>
       <c r="N495" s="5" t="n">
-        <v>0.000251</v>
+        <v>1.188404</v>
       </c>
       <c r="O495" s="5" t="n">
-        <v>-0.004053</v>
-      </c>
-      <c r="P495" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.372091</v>
+      </c>
+      <c r="P495" s="5" t="n">
+        <v>3.907874</v>
       </c>
       <c r="Q495" t="inlineStr">
         <is>
@@ -58322,10 +58342,14 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Other income/expense total</t>
-        </is>
-      </c>
-      <c r="D496" t="inlineStr"/>
+          <t>Foreign exchange gain (loss)</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E496" t="inlineStr">
         <is>
           <t>-</t>
@@ -58371,14 +58395,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N496" s="5" t="n">
-        <v>0.10784</v>
+      <c r="N496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O496" s="5" t="n">
-        <v>-2.133031</v>
+        <v>0.009826</v>
       </c>
       <c r="P496" s="5" t="n">
-        <v>2.11755</v>
+        <v>-0.033589</v>
       </c>
       <c r="Q496" t="inlineStr">
         <is>
@@ -58419,14 +58445,10 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Net loss for the year $</t>
-        </is>
-      </c>
-      <c r="D497" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Gain on royalty sale 7</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr"/>
       <c r="E497" t="inlineStr">
         <is>
           <t>-</t>
@@ -58472,14 +58494,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N497" s="5" t="n">
-        <v>-1.296244</v>
-      </c>
-      <c r="O497" s="5" t="n">
-        <v>-4.505122</v>
+      <c r="N497" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O497" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P497" s="5" t="n">
-        <v>-1.790324</v>
+        <v>2.140749</v>
       </c>
       <c r="Q497" t="inlineStr">
         <is>
@@ -58520,7 +58546,7 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>Cumulative translation adjustment</t>
+          <t>Interest and finance income (expense)</t>
         </is>
       </c>
       <c r="D498" t="inlineStr"/>
@@ -58569,14 +58595,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N498" s="5" t="n">
-        <v>0.041174</v>
+      <c r="N498" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O498" s="5" t="n">
-        <v>0.051481</v>
+        <v>-0.001849</v>
       </c>
       <c r="P498" s="5" t="n">
-        <v>-0.057607</v>
+        <v>0.01039</v>
       </c>
       <c r="Q498" t="inlineStr">
         <is>
@@ -58617,14 +58645,10 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D499" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Listing expense 5</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr"/>
       <c r="E499" t="inlineStr">
         <is>
           <t>-</t>
@@ -58670,14 +58694,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N499" s="5" t="n">
-        <v>-1.337418</v>
+      <c r="N499" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O499" s="5" t="n">
-        <v>-4.453641</v>
-      </c>
-      <c r="P499" s="5" t="n">
-        <v>-1.847931</v>
+        <v>-2.136955</v>
+      </c>
+      <c r="P499" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q499" t="inlineStr">
         <is>
@@ -58718,10 +58746,14 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>Basic and fully diluted loss per common share $</t>
-        </is>
-      </c>
-      <c r="D500" t="inlineStr"/>
+          <t>Other expenses</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E500" t="inlineStr">
         <is>
           <t>-</t>
@@ -58768,13 +58800,15 @@
         </is>
       </c>
       <c r="N500" s="5" t="n">
-        <v>9e-08</v>
+        <v>0.000251</v>
       </c>
       <c r="O500" s="5" t="n">
-        <v>-7e-08</v>
-      </c>
-      <c r="P500" s="5" t="n">
-        <v>-2e-08</v>
+        <v>-0.004053</v>
+      </c>
+      <c r="P500" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q500" t="inlineStr">
         <is>
@@ -58815,14 +58849,10 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
-        </is>
-      </c>
-      <c r="D501" t="inlineStr">
-        <is>
-          <t>SharesOutstanding</t>
-        </is>
-      </c>
+          <t>Other income/expense total</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr"/>
       <c r="E501" t="inlineStr">
         <is>
           <t>-</t>
@@ -58869,13 +58899,13 @@
         </is>
       </c>
       <c r="N501" s="5" t="n">
-        <v>14.825422</v>
+        <v>0.10784</v>
       </c>
       <c r="O501" s="5" t="n">
-        <v>67.61554</v>
+        <v>-2.133031</v>
       </c>
       <c r="P501" s="5" t="n">
-        <v>79.474881</v>
+        <v>2.11755</v>
       </c>
       <c r="Q501" t="inlineStr">
         <is>
@@ -58909,13 +58939,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B502" t="inlineStr"/>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>Other income/expense</t>
+        </is>
+      </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>December 31, 2018 December</t>
-        </is>
-      </c>
-      <c r="D502" t="inlineStr"/>
+          <t>Net loss for the year $</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E502" t="inlineStr">
         <is>
           <t>-</t>
@@ -58962,15 +59000,13 @@
         </is>
       </c>
       <c r="N502" s="5" t="n">
-        <v>0.002017</v>
+        <v>-1.296244</v>
       </c>
       <c r="O502" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="P502" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-4.505122</v>
+      </c>
+      <c r="P502" s="5" t="n">
+        <v>-1.790324</v>
       </c>
       <c r="Q502" t="inlineStr">
         <is>
@@ -59006,12 +59042,12 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income/expense</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Management fees and salaries 10</t>
+          <t>Cumulative translation adjustment</t>
         </is>
       </c>
       <c r="D503" t="inlineStr"/>
@@ -59061,15 +59097,13 @@
         </is>
       </c>
       <c r="N503" s="5" t="n">
-        <v>0.507</v>
+        <v>0.041174</v>
       </c>
       <c r="O503" s="5" t="n">
-        <v>0.552042</v>
-      </c>
-      <c r="P503" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.051481</v>
+      </c>
+      <c r="P503" s="5" t="n">
+        <v>-0.057607</v>
       </c>
       <c r="Q503" t="inlineStr">
         <is>
@@ -59110,10 +59144,14 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Interest and finance expense</t>
-        </is>
-      </c>
-      <c r="D504" t="inlineStr"/>
+          <t>Comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E504" t="inlineStr">
         <is>
           <t>-</t>
@@ -59160,15 +59198,13 @@
         </is>
       </c>
       <c r="N504" s="5" t="n">
-        <v>0.14798</v>
+        <v>-1.337418</v>
       </c>
       <c r="O504" s="5" t="n">
-        <v>0.001849</v>
-      </c>
-      <c r="P504" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-4.453641</v>
+      </c>
+      <c r="P504" s="5" t="n">
+        <v>-1.847931</v>
       </c>
       <c r="Q504" t="inlineStr">
         <is>
@@ -59209,14 +59245,10 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Foreign exchange (gain) loss</t>
-        </is>
-      </c>
-      <c r="D505" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Basic and fully diluted loss per common share $</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr"/>
       <c r="E505" t="inlineStr">
         <is>
           <t>-</t>
@@ -59263,15 +59295,13 @@
         </is>
       </c>
       <c r="N505" s="5" t="n">
-        <v>-0.040391</v>
+        <v>9e-08</v>
       </c>
       <c r="O505" s="5" t="n">
-        <v>-0.009826</v>
-      </c>
-      <c r="P505" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-7e-08</v>
+      </c>
+      <c r="P505" s="5" t="n">
+        <v>-2e-08</v>
       </c>
       <c r="Q505" t="inlineStr">
         <is>
@@ -59307,15 +59337,19 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Other income/expense</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Accounting and audit – Note 10 $</t>
-        </is>
-      </c>
-      <c r="D506" t="inlineStr"/>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
       <c r="E506" t="inlineStr">
         <is>
           <t>-</t>
@@ -59346,27 +59380,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K506" s="5" t="n">
-        <v>0.026434</v>
-      </c>
-      <c r="L506" s="5" t="n">
-        <v>0.029925</v>
-      </c>
-      <c r="M506" s="5" t="n">
-        <v>0.0519</v>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L506" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M506" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N506" s="5" t="n">
-        <v>0.06283</v>
-      </c>
-      <c r="O506" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P506" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>14.825422</v>
+      </c>
+      <c r="O506" s="5" t="n">
+        <v>67.61554</v>
+      </c>
+      <c r="P506" s="5" t="n">
+        <v>79.474881</v>
       </c>
       <c r="Q506" t="inlineStr">
         <is>
@@ -59400,21 +59436,13 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B507" t="inlineStr">
-        <is>
-          <t>EXPENSES</t>
-        </is>
-      </c>
+      <c r="B507" t="inlineStr"/>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Consulting fees – Note 10</t>
-        </is>
-      </c>
-      <c r="D507" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>December 31, 2018 December</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr"/>
       <c r="E507" t="inlineStr">
         <is>
           <t>-</t>
@@ -59445,22 +59473,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K507" s="5" t="n">
-        <v>0.001667</v>
-      </c>
-      <c r="L507" s="5" t="n">
-        <v>0.0145</v>
-      </c>
-      <c r="M507" s="5" t="n">
-        <v>0.04185</v>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L507" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M507" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N507" s="5" t="n">
-        <v>0.13417</v>
-      </c>
-      <c r="O507" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002017</v>
+      </c>
+      <c r="O507" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="P507" t="inlineStr">
         <is>
@@ -59501,12 +59533,12 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>Filing and listing fees</t>
+          <t>Management fees and salaries 10</t>
         </is>
       </c>
       <c r="D508" t="inlineStr"/>
@@ -59540,22 +59572,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K508" s="5" t="n">
-        <v>0.007379</v>
-      </c>
-      <c r="L508" s="5" t="n">
-        <v>0.01172</v>
-      </c>
-      <c r="M508" s="5" t="n">
-        <v>0.018845</v>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L508" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M508" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N508" s="5" t="n">
-        <v>0.018042</v>
-      </c>
-      <c r="O508" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.507</v>
+      </c>
+      <c r="O508" s="5" t="n">
+        <v>0.552042</v>
       </c>
       <c r="P508" t="inlineStr">
         <is>
@@ -59596,19 +59632,15 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Other income/expense</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Foreign exchange loss (gain)</t>
-        </is>
-      </c>
-      <c r="D509" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Interest and finance expense</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr"/>
       <c r="E509" t="inlineStr">
         <is>
           <t>-</t>
@@ -59649,16 +59681,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M509" s="5" t="n">
-        <v>-0.000577</v>
+      <c r="M509" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N509" s="5" t="n">
-        <v>0.000643</v>
-      </c>
-      <c r="O509" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.14798</v>
+      </c>
+      <c r="O509" s="5" t="n">
+        <v>0.001849</v>
       </c>
       <c r="P509" t="inlineStr">
         <is>
@@ -59699,53 +59731,69 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Other income/expense</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Foreign exchange (gain) loss</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E510" s="5" t="n">
-        <v>0.00325</v>
-      </c>
-      <c r="F510" s="5" t="n">
-        <v>0.0034</v>
-      </c>
-      <c r="G510" s="5" t="n">
-        <v>0.00325</v>
-      </c>
-      <c r="H510" s="5" t="n">
-        <v>0.0034</v>
-      </c>
-      <c r="I510" s="5" t="n">
-        <v>0.003808</v>
-      </c>
-      <c r="J510" s="5" t="n">
-        <v>0.004635</v>
-      </c>
-      <c r="K510" s="5" t="n">
-        <v>0.004714</v>
-      </c>
-      <c r="L510" s="5" t="n">
-        <v>0.003123</v>
-      </c>
-      <c r="M510" s="5" t="n">
-        <v>0.00125</v>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J510" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L510" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M510" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N510" s="5" t="n">
-        <v>0.013734</v>
-      </c>
-      <c r="O510" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.040391</v>
+      </c>
+      <c r="O510" s="5" t="n">
+        <v>-0.009826</v>
       </c>
       <c r="P510" t="inlineStr">
         <is>
@@ -59791,14 +59839,10 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Legal</t>
-        </is>
-      </c>
-      <c r="D511" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Accounting and audit – Note 10 $</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr"/>
       <c r="E511" t="inlineStr">
         <is>
           <t>-</t>
@@ -59830,16 +59874,16 @@
         </is>
       </c>
       <c r="K511" s="5" t="n">
-        <v>0.009089</v>
+        <v>0.026434</v>
       </c>
       <c r="L511" s="5" t="n">
-        <v>0.049503</v>
+        <v>0.029925</v>
       </c>
       <c r="M511" s="5" t="n">
-        <v>0.033664</v>
+        <v>0.0519</v>
       </c>
       <c r="N511" s="5" t="n">
-        <v>0.029098</v>
+        <v>0.06283</v>
       </c>
       <c r="O511" t="inlineStr">
         <is>
@@ -59890,7 +59934,7 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Management fees – Note 10</t>
+          <t>Consulting fees – Note 10</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
@@ -59928,19 +59972,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K512" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K512" s="5" t="n">
+        <v>0.001667</v>
       </c>
       <c r="L512" s="5" t="n">
-        <v>0.02</v>
+        <v>0.0145</v>
       </c>
       <c r="M512" s="5" t="n">
-        <v>0.05</v>
+        <v>0.04185</v>
       </c>
       <c r="N512" s="5" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.13417</v>
       </c>
       <c r="O512" t="inlineStr">
         <is>
@@ -59991,14 +60033,10 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="D513" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Filing and listing fees</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr"/>
       <c r="E513" t="inlineStr">
         <is>
           <t>-</t>
@@ -60029,21 +60067,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K513" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L513" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K513" s="5" t="n">
+        <v>0.007379</v>
+      </c>
+      <c r="L513" s="5" t="n">
+        <v>0.01172</v>
       </c>
       <c r="M513" s="5" t="n">
-        <v>0.121667</v>
+        <v>0.018845</v>
       </c>
       <c r="N513" s="5" t="n">
-        <v>0.220091</v>
+        <v>0.018042</v>
       </c>
       <c r="O513" t="inlineStr">
         <is>
@@ -60094,12 +60128,12 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Foreign exchange loss (gain)</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
@@ -60143,10 +60177,10 @@
         </is>
       </c>
       <c r="M514" s="5" t="n">
-        <v>0.012257</v>
+        <v>-0.000577</v>
       </c>
       <c r="N514" s="5" t="n">
-        <v>0.013349</v>
+        <v>0.000643</v>
       </c>
       <c r="O514" t="inlineStr">
         <is>
@@ -60197,7 +60231,7 @@
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>Rent – Note 10</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
@@ -60205,47 +60239,35 @@
           <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
-      <c r="E515" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F515" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G515" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H515" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I515" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J515" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E515" s="5" t="n">
+        <v>0.00325</v>
+      </c>
+      <c r="F515" s="5" t="n">
+        <v>0.0034</v>
+      </c>
+      <c r="G515" s="5" t="n">
+        <v>0.00325</v>
+      </c>
+      <c r="H515" s="5" t="n">
+        <v>0.0034</v>
+      </c>
+      <c r="I515" s="5" t="n">
+        <v>0.003808</v>
+      </c>
+      <c r="J515" s="5" t="n">
+        <v>0.004635</v>
       </c>
       <c r="K515" s="5" t="n">
-        <v>0.017873</v>
+        <v>0.004714</v>
       </c>
       <c r="L515" s="5" t="n">
-        <v>0.009187000000000001</v>
+        <v>0.003123</v>
       </c>
       <c r="M515" s="5" t="n">
-        <v>0.00435</v>
+        <v>0.00125</v>
       </c>
       <c r="N515" s="5" t="n">
-        <v>0.008892000000000001</v>
+        <v>0.013734</v>
       </c>
       <c r="O515" t="inlineStr">
         <is>
@@ -60296,12 +60318,12 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Shareholder communications</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>OtherOperatingExpenses</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
@@ -60334,21 +60356,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K516" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L516" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K516" s="5" t="n">
+        <v>0.009089</v>
+      </c>
+      <c r="L516" s="5" t="n">
+        <v>0.049503</v>
       </c>
       <c r="M516" s="5" t="n">
-        <v>0.024278</v>
+        <v>0.033664</v>
       </c>
       <c r="N516" s="5" t="n">
-        <v>0.016003</v>
+        <v>0.029098</v>
       </c>
       <c r="O516" t="inlineStr">
         <is>
@@ -60399,10 +60417,14 @@
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>Share-based compensation – Notes 9 and 10</t>
-        </is>
-      </c>
-      <c r="D517" t="inlineStr"/>
+          <t>Management fees – Note 10</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E517" t="inlineStr">
         <is>
           <t>-</t>
@@ -60439,13 +60461,13 @@
         </is>
       </c>
       <c r="L517" s="5" t="n">
-        <v>0.112</v>
+        <v>0.02</v>
       </c>
       <c r="M517" s="5" t="n">
-        <v>0.081</v>
+        <v>0.05</v>
       </c>
       <c r="N517" s="5" t="n">
-        <v>0.13</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="O517" t="inlineStr">
         <is>
@@ -60496,10 +60518,14 @@
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>Storage</t>
-        </is>
-      </c>
-      <c r="D518" t="inlineStr"/>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E518" t="inlineStr">
         <is>
           <t>-</t>
@@ -60530,17 +60556,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K518" s="5" t="n">
-        <v>0.006157</v>
-      </c>
-      <c r="L518" s="5" t="n">
-        <v>0.006398</v>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L518" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M518" s="5" t="n">
-        <v>0.001435</v>
+        <v>0.121667</v>
       </c>
       <c r="N518" s="5" t="n">
-        <v>0.001668</v>
+        <v>0.220091</v>
       </c>
       <c r="O518" t="inlineStr">
         <is>
@@ -60591,7 +60621,7 @@
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>Transfer agent</t>
+          <t>Office</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
@@ -60599,35 +60629,51 @@
           <t>OtherOperatingExpenses</t>
         </is>
       </c>
-      <c r="E519" s="5" t="n">
-        <v>0.005789</v>
-      </c>
-      <c r="F519" s="5" t="n">
-        <v>0.004833</v>
-      </c>
-      <c r="G519" s="5" t="n">
-        <v>0.004926</v>
-      </c>
-      <c r="H519" s="5" t="n">
-        <v>0.004797</v>
-      </c>
-      <c r="I519" s="5" t="n">
-        <v>0.004818</v>
-      </c>
-      <c r="J519" s="5" t="n">
-        <v>0.004889</v>
-      </c>
-      <c r="K519" s="5" t="n">
-        <v>0.005085</v>
-      </c>
-      <c r="L519" s="5" t="n">
-        <v>0.006841</v>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M519" s="5" t="n">
-        <v>0.011894</v>
+        <v>0.012257</v>
       </c>
       <c r="N519" s="5" t="n">
-        <v>0.009887</v>
+        <v>0.013349</v>
       </c>
       <c r="O519" t="inlineStr">
         <is>
@@ -60678,10 +60724,14 @@
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>Travel and entertainment</t>
-        </is>
-      </c>
-      <c r="D520" t="inlineStr"/>
+          <t>Rent – Note 10</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E520" t="inlineStr">
         <is>
           <t>-</t>
@@ -60712,21 +60762,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K520" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L520" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K520" s="5" t="n">
+        <v>0.017873</v>
+      </c>
+      <c r="L520" s="5" t="n">
+        <v>0.009187000000000001</v>
       </c>
       <c r="M520" s="5" t="n">
-        <v>0.007401</v>
+        <v>0.00435</v>
       </c>
       <c r="N520" s="5" t="n">
-        <v>0.005288</v>
+        <v>0.008892000000000001</v>
       </c>
       <c r="O520" t="inlineStr">
         <is>
@@ -60777,10 +60823,14 @@
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>Website</t>
-        </is>
-      </c>
-      <c r="D521" t="inlineStr"/>
+          <t>Shareholder communications</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E521" t="inlineStr">
         <is>
           <t>-</t>
@@ -60822,10 +60872,10 @@
         </is>
       </c>
       <c r="M521" s="5" t="n">
-        <v>0.006216</v>
+        <v>0.024278</v>
       </c>
       <c r="N521" s="5" t="n">
-        <v>0.002225</v>
+        <v>0.016003</v>
       </c>
       <c r="O521" t="inlineStr">
         <is>
@@ -60876,14 +60926,10 @@
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>EXPENSES total</t>
-        </is>
-      </c>
-      <c r="D522" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Share-based compensation – Notes 9 and 10</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr"/>
       <c r="E522" t="inlineStr">
         <is>
           <t>-</t>
@@ -60914,17 +60960,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K522" s="5" t="n">
-        <v>0.083971</v>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L522" s="5" t="n">
-        <v>0.284666</v>
+        <v>0.112</v>
       </c>
       <c r="M522" s="5" t="n">
-        <v>0.46743</v>
+        <v>0.081</v>
       </c>
       <c r="N522" s="5" t="n">
-        <v>0.73792</v>
+        <v>0.13</v>
       </c>
       <c r="O522" t="inlineStr">
         <is>
@@ -60970,12 +61018,12 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>Unrealized gain (loss) on marketable securities – Note 5</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="D523" t="inlineStr"/>
@@ -61009,21 +61057,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K523" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L523" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K523" s="5" t="n">
+        <v>0.006157</v>
+      </c>
+      <c r="L523" s="5" t="n">
+        <v>0.006398</v>
       </c>
       <c r="M523" s="5" t="n">
-        <v>0.00375</v>
+        <v>0.001435</v>
       </c>
       <c r="N523" s="5" t="n">
-        <v>-0.00375</v>
+        <v>0.001668</v>
       </c>
       <c r="O523" t="inlineStr">
         <is>
@@ -61069,62 +61113,48 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>Gain on sale of marketable securities – Note 5</t>
-        </is>
-      </c>
-      <c r="D524" t="inlineStr"/>
-      <c r="E524" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F524" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G524" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H524" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I524" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J524" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K524" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L524" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M524" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Transfer agent</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E524" s="5" t="n">
+        <v>0.005789</v>
+      </c>
+      <c r="F524" s="5" t="n">
+        <v>0.004833</v>
+      </c>
+      <c r="G524" s="5" t="n">
+        <v>0.004926</v>
+      </c>
+      <c r="H524" s="5" t="n">
+        <v>0.004797</v>
+      </c>
+      <c r="I524" s="5" t="n">
+        <v>0.004818</v>
+      </c>
+      <c r="J524" s="5" t="n">
+        <v>0.004889</v>
+      </c>
+      <c r="K524" s="5" t="n">
+        <v>0.005085</v>
+      </c>
+      <c r="L524" s="5" t="n">
+        <v>0.006841</v>
+      </c>
+      <c r="M524" s="5" t="n">
+        <v>0.011894</v>
       </c>
       <c r="N524" s="5" t="n">
-        <v>0.00099</v>
+        <v>0.009887</v>
       </c>
       <c r="O524" t="inlineStr">
         <is>
@@ -61170,12 +61200,12 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>Write-off of exploration and evaluation assets – Note 6</t>
+          <t>Travel and entertainment</t>
         </is>
       </c>
       <c r="D525" t="inlineStr"/>
@@ -61219,13 +61249,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M525" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M525" s="5" t="n">
+        <v>0.007401</v>
       </c>
       <c r="N525" s="5" t="n">
-        <v>-0.036901</v>
+        <v>0.005288</v>
       </c>
       <c r="O525" t="inlineStr">
         <is>
@@ -61271,12 +61299,12 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Other income - flow-through premium – Note 9</t>
+          <t>Website</t>
         </is>
       </c>
       <c r="D526" t="inlineStr"/>
@@ -61320,13 +61348,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M526" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M526" s="5" t="n">
+        <v>0.006216</v>
       </c>
       <c r="N526" s="5" t="n">
-        <v>0.032611</v>
+        <v>0.002225</v>
       </c>
       <c r="O526" t="inlineStr">
         <is>
@@ -61372,17 +61398,17 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year $</t>
+          <t>EXPENSES total</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
@@ -61415,21 +61441,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K527" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L527" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K527" s="5" t="n">
+        <v>0.083971</v>
+      </c>
+      <c r="L527" s="5" t="n">
+        <v>0.284666</v>
       </c>
       <c r="M527" s="5" t="n">
-        <v>-0.46368</v>
+        <v>0.46743</v>
       </c>
       <c r="N527" s="5" t="n">
-        <v>-0.74497</v>
+        <v>0.73792</v>
       </c>
       <c r="O527" t="inlineStr">
         <is>
@@ -61480,14 +61502,10 @@
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share $</t>
-        </is>
-      </c>
-      <c r="D528" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Unrealized gain (loss) on marketable securities – Note 5</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr"/>
       <c r="E528" t="inlineStr">
         <is>
           <t>-</t>
@@ -61529,10 +61547,10 @@
         </is>
       </c>
       <c r="M528" s="5" t="n">
-        <v>-1.8e-08</v>
+        <v>0.00375</v>
       </c>
       <c r="N528" s="5" t="n">
-        <v>-1.8e-08</v>
+        <v>-0.00375</v>
       </c>
       <c r="O528" t="inlineStr">
         <is>
@@ -61583,7 +61601,7 @@
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding – basic and diluted</t>
+          <t>Gain on sale of marketable securities – Note 5</t>
         </is>
       </c>
       <c r="D529" t="inlineStr"/>
@@ -61617,17 +61635,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K529" s="5" t="n">
-        <v>16.047239</v>
-      </c>
-      <c r="L529" s="5" t="n">
-        <v>17.694499</v>
-      </c>
-      <c r="M529" s="5" t="n">
-        <v>26.174124</v>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N529" s="5" t="n">
-        <v>40.959076</v>
+        <v>0.00099</v>
       </c>
       <c r="O529" t="inlineStr">
         <is>
@@ -61673,19 +61697,15 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>Foreign exchange</t>
-        </is>
-      </c>
-      <c r="D530" t="inlineStr">
-        <is>
-          <t>ForeignExchangeTradingGains</t>
-        </is>
-      </c>
+          <t>Write-off of exploration and evaluation assets – Note 6</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr"/>
       <c r="E530" t="inlineStr">
         <is>
           <t>-</t>
@@ -61726,13 +61746,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M530" s="5" t="n">
-        <v>-0.000577</v>
-      </c>
-      <c r="N530" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M530" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N530" s="5" t="n">
+        <v>-0.036901</v>
       </c>
       <c r="O530" t="inlineStr">
         <is>
@@ -61778,19 +61798,15 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>Office – Note 10</t>
-        </is>
-      </c>
-      <c r="D531" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Other income - flow-through premium – Note 9</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr"/>
       <c r="E531" t="inlineStr">
         <is>
           <t>-</t>
@@ -61821,19 +61837,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K531" s="5" t="n">
-        <v>0.005573</v>
-      </c>
-      <c r="L531" s="5" t="n">
-        <v>0.021469</v>
-      </c>
-      <c r="M531" s="5" t="n">
-        <v>0.012257</v>
-      </c>
-      <c r="N531" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L531" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M531" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N531" s="5" t="n">
+        <v>0.032611</v>
       </c>
       <c r="O531" t="inlineStr">
         <is>
@@ -61884,10 +61904,14 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Unrealized gain on marketable securities – Note 5</t>
-        </is>
-      </c>
-      <c r="D532" t="inlineStr"/>
+          <t>Loss and comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E532" t="inlineStr">
         <is>
           <t>-</t>
@@ -61929,12 +61953,10 @@
         </is>
       </c>
       <c r="M532" s="5" t="n">
-        <v>0.00375</v>
-      </c>
-      <c r="N532" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.46368</v>
+      </c>
+      <c r="N532" s="5" t="n">
+        <v>-0.74497</v>
       </c>
       <c r="O532" t="inlineStr">
         <is>
@@ -61985,10 +62007,14 @@
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>Gain on debt forgiven – Note 10</t>
-        </is>
-      </c>
-      <c r="D533" t="inlineStr"/>
+          <t>Basic and diluted loss per share $</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E533" t="inlineStr">
         <is>
           <t>-</t>
@@ -62024,18 +62050,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L533" s="5" t="n">
-        <v>0.362765</v>
-      </c>
-      <c r="M533" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N533" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L533" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M533" s="5" t="n">
+        <v>-1.8e-08</v>
+      </c>
+      <c r="N533" s="5" t="n">
+        <v>-1.8e-08</v>
       </c>
       <c r="O533" t="inlineStr">
         <is>
@@ -62086,7 +62110,7 @@
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>Flow-through premium – Note 9</t>
+          <t>Weighted average number of shares outstanding – basic and diluted</t>
         </is>
       </c>
       <c r="D534" t="inlineStr"/>
@@ -62120,23 +62144,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K534" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K534" s="5" t="n">
+        <v>16.047239</v>
       </c>
       <c r="L534" s="5" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="M534" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N534" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>17.694499</v>
+      </c>
+      <c r="M534" s="5" t="n">
+        <v>26.174124</v>
+      </c>
+      <c r="N534" s="5" t="n">
+        <v>40.959076</v>
       </c>
       <c r="O534" t="inlineStr">
         <is>
@@ -62182,15 +62200,19 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>Net and comprehensive income (loss) $</t>
-        </is>
-      </c>
-      <c r="D535" t="inlineStr"/>
+          <t>Foreign exchange</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>ForeignExchangeTradingGains</t>
+        </is>
+      </c>
       <c r="E535" t="inlineStr">
         <is>
           <t>-</t>
@@ -62221,14 +62243,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K535" s="5" t="n">
-        <v>-0.151996</v>
-      </c>
-      <c r="L535" s="5" t="n">
-        <v>0.08509899999999999</v>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L535" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M535" s="5" t="n">
-        <v>-0.46368</v>
+        <v>-0.000577</v>
       </c>
       <c r="N535" t="inlineStr">
         <is>
@@ -62279,17 +62305,17 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Basic and diluted income (loss) per share $</t>
+          <t>Office – Note 10</t>
         </is>
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>OtherOperatingExpenses</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
@@ -62323,13 +62349,13 @@
         </is>
       </c>
       <c r="K536" s="5" t="n">
-        <v>-9e-09</v>
+        <v>0.005573</v>
       </c>
       <c r="L536" s="5" t="n">
-        <v>5e-09</v>
+        <v>0.021469</v>
       </c>
       <c r="M536" s="5" t="n">
-        <v>-1.8e-08</v>
+        <v>0.012257</v>
       </c>
       <c r="N536" t="inlineStr">
         <is>
@@ -62380,12 +62406,12 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Share-based compensation – Notes 8 and 10</t>
+          <t>Unrealized gain on marketable securities – Note 5</t>
         </is>
       </c>
       <c r="D537" t="inlineStr"/>
@@ -62424,13 +62450,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L537" s="5" t="n">
-        <v>0.112</v>
-      </c>
-      <c r="M537" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L537" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M537" s="5" t="n">
+        <v>0.00375</v>
       </c>
       <c r="N537" t="inlineStr">
         <is>
@@ -62486,7 +62512,7 @@
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>Loss on write-off of exploration and evaluation assets – Note 7</t>
+          <t>Gain on debt forgiven – Note 10</t>
         </is>
       </c>
       <c r="D538" t="inlineStr"/>
@@ -62520,13 +62546,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K538" s="5" t="n">
-        <v>-0.068025</v>
-      </c>
-      <c r="L538" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L538" s="5" t="n">
+        <v>0.362765</v>
       </c>
       <c r="M538" t="inlineStr">
         <is>
@@ -62587,7 +62613,7 @@
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>Flow-through premium – Note 8</t>
+          <t>Flow-through premium – Note 9</t>
         </is>
       </c>
       <c r="D539" t="inlineStr"/>
@@ -62683,45 +62709,53 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>Administration $</t>
+          <t>Net and comprehensive income (loss) $</t>
         </is>
       </c>
       <c r="D540" t="inlineStr"/>
-      <c r="E540" s="5" t="n">
-        <v>0.037332</v>
-      </c>
-      <c r="F540" s="5" t="n">
-        <v>0.012283</v>
-      </c>
-      <c r="G540" s="5" t="n">
-        <v>0.03139</v>
-      </c>
-      <c r="H540" s="5" t="n">
-        <v>0.024956</v>
-      </c>
-      <c r="I540" s="5" t="n">
-        <v>0.025648</v>
-      </c>
-      <c r="J540" s="5" t="n">
-        <v>0.023985</v>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K540" s="5" t="n">
-        <v>0.029661</v>
-      </c>
-      <c r="L540" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M540" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.151996</v>
+      </c>
+      <c r="L540" s="5" t="n">
+        <v>0.08509899999999999</v>
+      </c>
+      <c r="M540" s="5" t="n">
+        <v>-0.46368</v>
       </c>
       <c r="N540" t="inlineStr">
         <is>
@@ -62772,45 +62806,57 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>Audit &amp; accounting fees</t>
-        </is>
-      </c>
-      <c r="D541" t="inlineStr"/>
-      <c r="E541" s="5" t="n">
-        <v>0.0234</v>
-      </c>
-      <c r="F541" s="5" t="n">
-        <v>0.025048</v>
-      </c>
-      <c r="G541" s="5" t="n">
-        <v>0.02281</v>
-      </c>
-      <c r="H541" s="5" t="n">
-        <v>0.021056</v>
-      </c>
-      <c r="I541" s="5" t="n">
-        <v>0.02942</v>
-      </c>
-      <c r="J541" s="5" t="n">
-        <v>0.026715</v>
+          <t>Basic and diluted income (loss) per share $</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K541" s="5" t="n">
-        <v>0.026434</v>
-      </c>
-      <c r="L541" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M541" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-9e-09</v>
+      </c>
+      <c r="L541" s="5" t="n">
+        <v>5e-09</v>
+      </c>
+      <c r="M541" s="5" t="n">
+        <v>-1.8e-08</v>
       </c>
       <c r="N541" t="inlineStr">
         <is>
@@ -62866,7 +62912,7 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Director’s fees (Note 12)</t>
+          <t>Share-based compensation – Notes 8 and 10</t>
         </is>
       </c>
       <c r="D542" t="inlineStr"/>
@@ -62895,16 +62941,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J542" s="5" t="n">
-        <v>0.003333</v>
-      </c>
-      <c r="K542" s="5" t="n">
-        <v>0.001667</v>
-      </c>
-      <c r="L542" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J542" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L542" s="5" t="n">
+        <v>0.112</v>
       </c>
       <c r="M542" t="inlineStr">
         <is>
@@ -62960,39 +63008,47 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>Filing fees</t>
-        </is>
-      </c>
-      <c r="D543" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E543" s="5" t="n">
-        <v>0.011431</v>
-      </c>
-      <c r="F543" s="5" t="n">
-        <v>0.010573</v>
-      </c>
-      <c r="G543" s="5" t="n">
-        <v>0.008057</v>
-      </c>
-      <c r="H543" s="5" t="n">
-        <v>0.010896</v>
-      </c>
-      <c r="I543" s="5" t="n">
-        <v>0.009351</v>
-      </c>
-      <c r="J543" s="5" t="n">
-        <v>0.008194999999999999</v>
+          <t>Loss on write-off of exploration and evaluation assets – Note 7</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr"/>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K543" s="5" t="n">
-        <v>0.007379</v>
+        <v>-0.068025</v>
       </c>
       <c r="L543" t="inlineStr">
         <is>
@@ -63053,44 +63109,52 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>Legal fees</t>
-        </is>
-      </c>
-      <c r="D544" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E544" s="5" t="n">
-        <v>0.029101</v>
-      </c>
-      <c r="F544" s="5" t="n">
-        <v>0.017573</v>
-      </c>
-      <c r="G544" s="5" t="n">
-        <v>0.027976</v>
-      </c>
-      <c r="H544" s="5" t="n">
-        <v>0.018147</v>
-      </c>
-      <c r="I544" s="5" t="n">
-        <v>0.018398</v>
-      </c>
-      <c r="J544" s="5" t="n">
-        <v>0.01269</v>
-      </c>
-      <c r="K544" s="5" t="n">
-        <v>0.009089</v>
-      </c>
-      <c r="L544" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Flow-through premium – Note 8</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr"/>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L544" s="5" t="n">
+        <v>0.007</v>
       </c>
       <c r="M544" t="inlineStr">
         <is>
@@ -63151,36 +63215,30 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D545" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Administration $</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr"/>
       <c r="E545" s="5" t="n">
-        <v>6.999999999999999e-05</v>
+        <v>0.037332</v>
       </c>
       <c r="F545" s="5" t="n">
-        <v>0.000114</v>
+        <v>0.012283</v>
       </c>
       <c r="G545" s="5" t="n">
-        <v>6.9e-05</v>
-      </c>
-      <c r="H545" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.03139</v>
+      </c>
+      <c r="H545" s="5" t="n">
+        <v>0.024956</v>
       </c>
       <c r="I545" s="5" t="n">
-        <v>0.000132</v>
+        <v>0.025648</v>
       </c>
       <c r="J545" s="5" t="n">
-        <v>-2.9e-05</v>
+        <v>0.023985</v>
       </c>
       <c r="K545" s="5" t="n">
-        <v>-5.8e-05</v>
+        <v>0.029661</v>
       </c>
       <c r="L545" t="inlineStr">
         <is>
@@ -63246,40 +63304,30 @@
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>Write-down (Recovery) of exploration and evaluation assets</t>
+          <t>Audit &amp; accounting fees</t>
         </is>
       </c>
       <c r="D546" t="inlineStr"/>
-      <c r="E546" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F546" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G546" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H546" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I546" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E546" s="5" t="n">
+        <v>0.0234</v>
+      </c>
+      <c r="F546" s="5" t="n">
+        <v>0.025048</v>
+      </c>
+      <c r="G546" s="5" t="n">
+        <v>0.02281</v>
+      </c>
+      <c r="H546" s="5" t="n">
+        <v>0.021056</v>
+      </c>
+      <c r="I546" s="5" t="n">
+        <v>0.02942</v>
       </c>
       <c r="J546" s="5" t="n">
-        <v>-0.025</v>
+        <v>0.026715</v>
       </c>
       <c r="K546" s="5" t="n">
-        <v>0.068025</v>
+        <v>0.026434</v>
       </c>
       <c r="L546" t="inlineStr">
         <is>
@@ -63345,12 +63393,12 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>Net Loss and Comprehensive Loss for the Year $</t>
+          <t>Director’s fees (Note 12)</t>
         </is>
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
@@ -63373,14 +63421,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I547" s="5" t="n">
-        <v>-0.020479</v>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J547" s="5" t="n">
-        <v>-0.059413</v>
+        <v>0.003333</v>
       </c>
       <c r="K547" s="5" t="n">
-        <v>-0.151996</v>
+        <v>0.001667</v>
       </c>
       <c r="L547" t="inlineStr">
         <is>
@@ -63446,34 +63496,34 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>Basic and Fully Diluted Loss Per Share $</t>
+          <t>Filing fees</t>
         </is>
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E548" s="5" t="n">
-        <v>-3.1e-08</v>
+        <v>0.011431</v>
       </c>
       <c r="F548" s="5" t="n">
-        <v>-3e-09</v>
+        <v>0.010573</v>
       </c>
       <c r="G548" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.008057</v>
       </c>
       <c r="H548" s="5" t="n">
-        <v>-4e-08</v>
+        <v>0.010896</v>
       </c>
       <c r="I548" s="5" t="n">
-        <v>-1e-09</v>
+        <v>0.009351</v>
       </c>
       <c r="J548" s="5" t="n">
-        <v>-4e-09</v>
+        <v>0.008194999999999999</v>
       </c>
       <c r="K548" s="5" t="n">
-        <v>-9e-09</v>
+        <v>0.007379</v>
       </c>
       <c r="L548" t="inlineStr">
         <is>
@@ -63539,34 +63589,34 @@
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>Weighted Average Number of Shares Outstanding – basic and diluted</t>
-        </is>
-      </c>
-      <c r="D549" t="inlineStr"/>
-      <c r="E549" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F549" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Legal fees</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E549" s="5" t="n">
+        <v>0.029101</v>
+      </c>
+      <c r="F549" s="5" t="n">
+        <v>0.017573</v>
       </c>
       <c r="G549" s="5" t="n">
-        <v>15.499886</v>
+        <v>0.027976</v>
       </c>
       <c r="H549" s="5" t="n">
-        <v>16.047239</v>
+        <v>0.018147</v>
       </c>
       <c r="I549" s="5" t="n">
-        <v>16.047239</v>
+        <v>0.018398</v>
       </c>
       <c r="J549" s="5" t="n">
-        <v>16.047239</v>
+        <v>0.01269</v>
       </c>
       <c r="K549" s="5" t="n">
-        <v>16.047239</v>
+        <v>0.009089</v>
       </c>
       <c r="L549" t="inlineStr">
         <is>
@@ -63632,34 +63682,36 @@
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Directors’ fees</t>
-        </is>
-      </c>
-      <c r="D550" t="inlineStr"/>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E550" s="5" t="n">
-        <v>0.001</v>
+        <v>6.999999999999999e-05</v>
       </c>
       <c r="F550" s="5" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="G550" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H550" s="5" t="n">
-        <v>0.000833</v>
+        <v>0.000114</v>
+      </c>
+      <c r="G550" s="5" t="n">
+        <v>6.9e-05</v>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I550" s="5" t="n">
-        <v>0.002167</v>
+        <v>0.000132</v>
       </c>
       <c r="J550" s="5" t="n">
-        <v>0.003333</v>
-      </c>
-      <c r="K550" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.9e-05</v>
+      </c>
+      <c r="K550" s="5" t="n">
+        <v>-5.8e-05</v>
       </c>
       <c r="L550" t="inlineStr">
         <is>
@@ -63725,36 +63777,40 @@
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>Net loss before other items</t>
-        </is>
-      </c>
-      <c r="D551" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
-      <c r="E551" s="5" t="n">
-        <v>-0.439945</v>
-      </c>
-      <c r="F551" s="5" t="n">
-        <v>-0.039857</v>
-      </c>
-      <c r="G551" s="5" t="n">
-        <v>-0.14695</v>
-      </c>
-      <c r="H551" s="5" t="n">
-        <v>-0.086257</v>
-      </c>
-      <c r="I551" s="5" t="n">
-        <v>-0.09361</v>
+          <t>Write-down (Recovery) of exploration and evaluation assets</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr"/>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J551" s="5" t="n">
-        <v>-0.084442</v>
-      </c>
-      <c r="K551" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.025</v>
+      </c>
+      <c r="K551" s="5" t="n">
+        <v>0.068025</v>
       </c>
       <c r="L551" t="inlineStr">
         <is>
@@ -63820,10 +63876,14 @@
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>Gain on mineral property option payments</t>
-        </is>
-      </c>
-      <c r="D552" t="inlineStr"/>
+          <t>Net Loss and Comprehensive Loss for the Year $</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E552" t="inlineStr">
         <is>
           <t>-</t>
@@ -63845,15 +63905,13 @@
         </is>
       </c>
       <c r="I552" s="5" t="n">
-        <v>0.07299899999999999</v>
+        <v>-0.020479</v>
       </c>
       <c r="J552" s="5" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="K552" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.059413</v>
+      </c>
+      <c r="K552" s="5" t="n">
+        <v>-0.151996</v>
       </c>
       <c r="L552" t="inlineStr">
         <is>
@@ -63919,40 +63977,34 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>Interest expense (Note 10)</t>
+          <t>Basic and Fully Diluted Loss Per Share $</t>
         </is>
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>InterestExpenseOperating</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E553" s="5" t="n">
-        <v>0.005398</v>
+        <v>-3.1e-08</v>
       </c>
       <c r="F553" s="5" t="n">
-        <v>0.002307</v>
+        <v>-3e-09</v>
       </c>
       <c r="G553" s="5" t="n">
-        <v>0.001024</v>
+        <v>-1e-08</v>
       </c>
       <c r="H553" s="5" t="n">
-        <v>0.002172</v>
-      </c>
-      <c r="I553" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J553" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K553" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-4e-08</v>
+      </c>
+      <c r="I553" s="5" t="n">
+        <v>-1e-09</v>
+      </c>
+      <c r="J553" s="5" t="n">
+        <v>-4e-09</v>
+      </c>
+      <c r="K553" s="5" t="n">
+        <v>-9e-09</v>
       </c>
       <c r="L553" t="inlineStr">
         <is>
@@ -64018,44 +64070,34 @@
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>Management fees</t>
-        </is>
-      </c>
-      <c r="D554" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Weighted Average Number of Shares Outstanding – basic and diluted</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr"/>
       <c r="E554" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F554" s="5" t="n">
-        <v>0.01284</v>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G554" s="5" t="n">
-        <v>0.00321</v>
-      </c>
-      <c r="H554" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I554" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J554" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K554" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>15.499886</v>
+      </c>
+      <c r="H554" s="5" t="n">
+        <v>16.047239</v>
+      </c>
+      <c r="I554" s="5" t="n">
+        <v>16.047239</v>
+      </c>
+      <c r="J554" s="5" t="n">
+        <v>16.047239</v>
+      </c>
+      <c r="K554" s="5" t="n">
+        <v>16.047239</v>
       </c>
       <c r="L554" t="inlineStr">
         <is>
@@ -64121,35 +64163,33 @@
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>Stock based compensation</t>
-        </is>
-      </c>
-      <c r="D555" t="inlineStr"/>
+          <t>Directors’ fees</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E555" s="5" t="n">
-        <v>0.373182</v>
-      </c>
-      <c r="F555" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G555" s="5" t="n">
-        <v>0.044307</v>
-      </c>
-      <c r="H555" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I555" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J555" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.001</v>
+      </c>
+      <c r="F555" s="5" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H555" s="5" t="n">
+        <v>0.000833</v>
+      </c>
+      <c r="I555" s="5" t="n">
+        <v>0.002167</v>
+      </c>
+      <c r="J555" s="5" t="n">
+        <v>0.003333</v>
       </c>
       <c r="K555" t="inlineStr">
         <is>
@@ -64220,37 +64260,31 @@
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>Write-down of mineral properties</t>
-        </is>
-      </c>
-      <c r="D556" t="inlineStr"/>
-      <c r="E556" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F556" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G556" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss before other items</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E556" s="5" t="n">
+        <v>-0.439945</v>
+      </c>
+      <c r="F556" s="5" t="n">
+        <v>-0.039857</v>
+      </c>
+      <c r="G556" s="5" t="n">
+        <v>-0.14695</v>
       </c>
       <c r="H556" s="5" t="n">
-        <v>-0.606119</v>
-      </c>
-      <c r="I556" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J556" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.086257</v>
+      </c>
+      <c r="I556" s="5" t="n">
+        <v>-0.09361</v>
+      </c>
+      <c r="J556" s="5" t="n">
+        <v>-0.084442</v>
       </c>
       <c r="K556" t="inlineStr">
         <is>
@@ -64321,35 +64355,35 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>Net Loss and Comprehensive Loss for the Year</t>
-        </is>
-      </c>
-      <c r="D557" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E557" s="5" t="n">
-        <v>-0.439875</v>
-      </c>
-      <c r="F557" s="5" t="n">
-        <v>-0.039743</v>
-      </c>
-      <c r="G557" s="5" t="n">
-        <v>-0.146881</v>
-      </c>
-      <c r="H557" s="5" t="n">
-        <v>-0.692376</v>
-      </c>
-      <c r="I557" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J557" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Gain on mineral property option payments</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr"/>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I557" s="5" t="n">
+        <v>0.07299899999999999</v>
+      </c>
+      <c r="J557" s="5" t="n">
+        <v>0.025</v>
       </c>
       <c r="K557" t="inlineStr">
         <is>
@@ -64420,21 +64454,25 @@
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>Deficit – Beginning of the Year</t>
-        </is>
-      </c>
-      <c r="D558" t="inlineStr"/>
+          <t>Interest expense (Note 10)</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
       <c r="E558" s="5" t="n">
-        <v>-4.503741</v>
+        <v>0.005398</v>
       </c>
       <c r="F558" s="5" t="n">
-        <v>-4.943616</v>
+        <v>0.002307</v>
       </c>
       <c r="G558" s="5" t="n">
-        <v>-4.983359</v>
+        <v>0.001024</v>
       </c>
       <c r="H558" s="5" t="n">
-        <v>-5.13024</v>
+        <v>0.002172</v>
       </c>
       <c r="I558" t="inlineStr">
         <is>
@@ -64515,21 +64553,29 @@
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>Deficit – End of the Year $</t>
-        </is>
-      </c>
-      <c r="D559" t="inlineStr"/>
-      <c r="E559" s="5" t="n">
-        <v>-4.943616</v>
+          <t>Management fees</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F559" s="5" t="n">
-        <v>-4.983359</v>
+        <v>0.01284</v>
       </c>
       <c r="G559" s="5" t="n">
-        <v>-5.13024</v>
-      </c>
-      <c r="H559" s="5" t="n">
-        <v>-5.822616</v>
+        <v>0.00321</v>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I559" t="inlineStr">
         <is>
@@ -64610,22 +64656,20 @@
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>Recovery of mineral property costs previously written off (Note 4 (b))</t>
+          <t>Stock based compensation</t>
         </is>
       </c>
       <c r="D560" t="inlineStr"/>
-      <c r="E560" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F560" s="5" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="G560" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E560" s="5" t="n">
+        <v>0.373182</v>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G560" s="5" t="n">
+        <v>0.044307</v>
       </c>
       <c r="H560" t="inlineStr">
         <is>
@@ -64711,27 +64755,27 @@
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>Weighted Average Number of Shares Outstanding</t>
-        </is>
-      </c>
-      <c r="D561" t="inlineStr">
-        <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
-      <c r="E561" s="5" t="n">
-        <v>14.178346</v>
-      </c>
-      <c r="F561" s="5" t="n">
-        <v>15.028147</v>
-      </c>
-      <c r="G561" s="5" t="n">
-        <v>15.499886</v>
-      </c>
-      <c r="H561" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Write-down of mineral properties</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr"/>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H561" s="5" t="n">
+        <v>-0.606119</v>
       </c>
       <c r="I561" t="inlineStr">
         <is>
@@ -64812,87 +64856,578 @@
       </c>
       <c r="C562" t="inlineStr">
         <is>
+          <t>Net Loss and Comprehensive Loss for the Year</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E562" s="5" t="n">
+        <v>-0.439875</v>
+      </c>
+      <c r="F562" s="5" t="n">
+        <v>-0.039743</v>
+      </c>
+      <c r="G562" s="5" t="n">
+        <v>-0.146881</v>
+      </c>
+      <c r="H562" s="5" t="n">
+        <v>-0.692376</v>
+      </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>Deficit – Beginning of the Year</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr"/>
+      <c r="E563" s="5" t="n">
+        <v>-4.503741</v>
+      </c>
+      <c r="F563" s="5" t="n">
+        <v>-4.943616</v>
+      </c>
+      <c r="G563" s="5" t="n">
+        <v>-4.983359</v>
+      </c>
+      <c r="H563" s="5" t="n">
+        <v>-5.13024</v>
+      </c>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J563" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L563" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M563" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N563" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O563" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P563" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q563" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R563" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S563" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T563" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U563" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>Deficit – End of the Year $</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr"/>
+      <c r="E564" s="5" t="n">
+        <v>-4.943616</v>
+      </c>
+      <c r="F564" s="5" t="n">
+        <v>-4.983359</v>
+      </c>
+      <c r="G564" s="5" t="n">
+        <v>-5.13024</v>
+      </c>
+      <c r="H564" s="5" t="n">
+        <v>-5.822616</v>
+      </c>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J564" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L564" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M564" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N564" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O564" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P564" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q564" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R564" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S564" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T564" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U564" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>Recovery of mineral property costs previously written off (Note 4 (b))</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr"/>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F565" s="5" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>Weighted Average Number of Shares Outstanding</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E566" s="5" t="n">
+        <v>14.178346</v>
+      </c>
+      <c r="F566" s="5" t="n">
+        <v>15.028147</v>
+      </c>
+      <c r="G566" s="5" t="n">
+        <v>15.499886</v>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J566" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L566" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M566" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N566" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O566" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P566" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q566" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R566" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S566" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T566" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U566" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
           <t>(b))</t>
         </is>
       </c>
-      <c r="D562" t="inlineStr"/>
-      <c r="E562" s="5" t="n">
+      <c r="D567" t="inlineStr"/>
+      <c r="E567" s="5" t="n">
         <v>-0.049938</v>
       </c>
-      <c r="F562" s="5" t="n">
+      <c r="F567" s="5" t="n">
         <v>-0.05</v>
       </c>
-      <c r="G562" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H562" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I562" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J562" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K562" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L562" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M562" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N562" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O562" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P562" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q562" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R562" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S562" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T562" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U562" t="inlineStr">
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J567" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L567" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M567" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N567" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O567" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P567" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q567" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R567" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S567" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T567" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U567" t="inlineStr">
         <is>
           <t>-</t>
         </is>
